--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A495C6A-BF14-44B8-A139-5DF114D46939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F15D77-D0DC-404B-AF29-66E386CE219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
     <sheet name="Top" sheetId="3" r:id="rId2"/>
+    <sheet name="MOUSER ZAMÓWIENIE 1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="245">
+  <si>
+    <t>Ilość</t>
+  </si>
   <si>
     <t>Ref</t>
   </si>
@@ -556,9 +560,6 @@
     <t>Connector_PinHeader_2.54mm:PinHeader_1x02_P2.54mm_Vertical_SMD_Pin1Left</t>
   </si>
   <si>
-    <t>Connector_Molex:Molex_PicoBlade_53047-0210_1x02_P1.25mm_Vertical</t>
-  </si>
-  <si>
     <t>Connector_Molex:Molex_PicoBlade_53048-0210_1x02_P1.25mm_Horizontal</t>
   </si>
   <si>
@@ -586,9 +587,6 @@
     <t>MX-503398-1892</t>
   </si>
   <si>
-    <t>UBC-RA-TF</t>
-  </si>
-  <si>
     <t>10164227-1001A1RLF</t>
   </si>
   <si>
@@ -604,9 +602,6 @@
     <t>TODO: to ma być gniazdo</t>
   </si>
   <si>
-    <t>53047-0210</t>
-  </si>
-  <si>
     <t>53048-0210</t>
   </si>
   <si>
@@ -616,9 +611,6 @@
     <t>MBR1020VL-AU-R1</t>
   </si>
   <si>
-    <t>MX-53047-0210</t>
-  </si>
-  <si>
     <t>MX-53048-0210</t>
   </si>
   <si>
@@ -709,9 +701,6 @@
     <t>Tantalum, Kemet-B, 22uF@10V min.</t>
   </si>
   <si>
-    <t>Tantalum, Kemet-B, 10uF@35V min.</t>
-  </si>
-  <si>
     <t>Kemet-D, 10V</t>
   </si>
   <si>
@@ -721,18 +710,9 @@
     <t>TAJD106K035R</t>
   </si>
   <si>
-    <t>UBC-RA-TF*</t>
-  </si>
-  <si>
     <t>* - equivalent</t>
   </si>
   <si>
-    <t>LTST-C190KRKT*</t>
-  </si>
-  <si>
-    <t>LTST-C190KGKT*</t>
-  </si>
-  <si>
     <t>Not necessary, if no SD card is used</t>
   </si>
   <si>
@@ -749,6 +729,72 @@
   </si>
   <si>
     <t>SUMA / płytka</t>
+  </si>
+  <si>
+    <t>Tantalum, Kemet-C, 10uF@35V min.</t>
+  </si>
+  <si>
+    <t>Capacitor_Tantalum_SMD:CP_EIA-3528-21_Kemet-C_HandSolder</t>
+  </si>
+  <si>
+    <t>TAJC106K035R</t>
+  </si>
+  <si>
+    <t>LTST-C190KRKT (substitute)</t>
+  </si>
+  <si>
+    <t>LTST-C190KGKT (substitute)</t>
+  </si>
+  <si>
+    <t>USB4105-GF-A-060 (substitute)</t>
+  </si>
+  <si>
+    <t>Will be unused</t>
+  </si>
+  <si>
+    <t>ZL303-2X40P</t>
+  </si>
+  <si>
+    <t>Zwory do J2</t>
+  </si>
+  <si>
+    <t>JUMPER-2.0/B</t>
+  </si>
+  <si>
+    <t>MX-53047-0310</t>
+  </si>
+  <si>
+    <t>53047-0310</t>
+  </si>
+  <si>
+    <t>Connector_Molex:Molex_PicoBlade_53047-0310_1x03_P1.25mm_Vertical</t>
+  </si>
+  <si>
+    <t>LoRa - Antena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">713-114993390 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">835-RT9742GGJ5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">652-SRN8040HA-3R6M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">538-46765-1301 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">798-FH12-22S-0.5SH55 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTX150P116B08683 </t>
+  </si>
+  <si>
+    <t>!!!!!!!!!!!!</t>
+  </si>
+  <si>
+    <t>Kod</t>
   </si>
 </sst>
 </file>
@@ -783,7 +829,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -793,6 +839,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1430,9 +1482,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1454,14 +1507,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1471,47 +1526,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -1525,42 +1580,44 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="8" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="44" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1896,113 +1953,113 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8129CC7-4966-44CA-8216-6BC45B8BB38E}">
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="14" style="25" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" style="25" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="17" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="26" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="12" customWidth="1"/>
-    <col min="10" max="10" width="30.140625" style="34" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="14" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14" style="28" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="20" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="29" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="15" customWidth="1"/>
+    <col min="10" max="10" width="30.140625" style="37" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="30.140625" style="18" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="34"/>
+      <c r="K1" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="39"/>
+    </row>
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="77"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="67" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="27"/>
-      <c r="I1" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="L1" s="36"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="64" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="66" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="K2" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="69" t="s">
-        <v>130</v>
+      <c r="I2" s="69" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="70" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="72" t="s">
+        <v>131</v>
       </c>
       <c r="M2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="42">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="41" t="s">
+      <c r="B3" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="47">
+      <c r="C3" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="50">
         <v>3.9190000000000003E-2</v>
       </c>
-      <c r="L3" s="71" t="s">
-        <v>199</v>
+      <c r="L3" s="74" t="s">
+        <v>196</v>
       </c>
       <c r="M3">
         <v>12</v>
@@ -2013,29 +2070,29 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="23" t="s">
+      <c r="B4" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="14">
+      <c r="C4" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K4" s="17">
         <v>0.20480000000000001</v>
       </c>
-      <c r="L4" s="60" t="s">
-        <v>194</v>
+      <c r="L4" s="63" t="s">
+        <v>191</v>
       </c>
       <c r="M4">
         <v>12</v>
@@ -2046,29 +2103,29 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="8">
         <v>1</v>
       </c>
-      <c r="B5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K5" s="14">
+      <c r="C5" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="17">
         <v>0.18210000000000001</v>
       </c>
-      <c r="L5" s="60" t="s">
-        <v>193</v>
+      <c r="L5" s="63" t="s">
+        <v>190</v>
       </c>
       <c r="M5">
         <v>12</v>
@@ -2079,29 +2136,29 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="8">
         <v>1</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="23" t="s">
+      <c r="B6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K6" s="14">
+      <c r="C6" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="17">
         <v>0.1421</v>
       </c>
-      <c r="L6" s="60" t="s">
-        <v>195</v>
+      <c r="L6" s="63" t="s">
+        <v>192</v>
       </c>
       <c r="M6">
         <v>12</v>
@@ -2112,29 +2169,29 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="B7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K7" s="14">
+      <c r="C7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="17">
         <v>4.1669999999999999E-2</v>
       </c>
-      <c r="L7" s="60" t="s">
-        <v>196</v>
+      <c r="L7" s="63" t="s">
+        <v>193</v>
       </c>
       <c r="M7">
         <v>12</v>
@@ -2145,29 +2202,29 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>4</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="B8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="14">
+      <c r="C8" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="17">
         <v>0.28220000000000001</v>
       </c>
-      <c r="L8" s="60" t="s">
-        <v>197</v>
+      <c r="L8" s="63" t="s">
+        <v>194</v>
       </c>
       <c r="M8">
         <v>42</v>
@@ -2178,29 +2235,29 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="8">
         <v>3</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="B9" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="C9" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K9" s="17">
         <v>3.3119999999999997E-2</v>
       </c>
-      <c r="L9" s="60" t="s">
-        <v>202</v>
+      <c r="L9" s="63" t="s">
+        <v>199</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -2211,29 +2268,29 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="8">
         <v>4</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="B10" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K10" s="14">
+      <c r="C10" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="17">
         <v>3.9050000000000001E-2</v>
       </c>
-      <c r="L10" s="60" t="s">
-        <v>203</v>
+      <c r="L10" s="63" t="s">
+        <v>200</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -2244,29 +2301,29 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="8">
         <v>2</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K11" s="14">
+      <c r="C11" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" s="17">
         <v>1.7569999999999999E-2</v>
       </c>
-      <c r="L11" s="60" t="s">
-        <v>204</v>
+      <c r="L11" s="63" t="s">
+        <v>201</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -2277,29 +2334,29 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="23" t="s">
+      <c r="B12" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K12" s="14">
+      <c r="C12" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="17">
         <v>3.6560000000000002E-2</v>
       </c>
-      <c r="L12" s="60" t="s">
-        <v>205</v>
+      <c r="L12" s="63" t="s">
+        <v>202</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -2310,29 +2367,29 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K13" s="14">
+      <c r="C13" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="17">
         <v>0.21560000000000001</v>
       </c>
-      <c r="L13" s="60" t="s">
-        <v>192</v>
+      <c r="L13" s="63" t="s">
+        <v>189</v>
       </c>
       <c r="M13">
         <v>12</v>
@@ -2343,29 +2400,29 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="23" t="s">
+      <c r="B14" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K14" s="14">
+      <c r="C14" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K14" s="17">
         <v>5.9389999999999998E-2</v>
       </c>
-      <c r="L14" s="60" t="s">
-        <v>201</v>
+      <c r="L14" s="63" t="s">
+        <v>198</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -2376,29 +2433,29 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="C15" s="23" t="s">
+      <c r="B15" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K15" s="14">
+      <c r="C15" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="17">
         <v>6.7129999999999995E-2</v>
       </c>
-      <c r="L15" s="60" t="s">
-        <v>200</v>
+      <c r="L15" s="63" t="s">
+        <v>197</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -2409,860 +2466,969 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>134</v>
+      <c r="C16" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>229</v>
       </c>
       <c r="M16" s="1"/>
+      <c r="N16" s="1">
+        <f t="shared" ref="N16:N19" si="1">K16*M16</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="8">
         <v>1</v>
       </c>
-      <c r="B17" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="23" t="s">
+      <c r="B17" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>134</v>
+      <c r="C17" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1.093</v>
+      </c>
+      <c r="L17" s="79" t="s">
+        <v>230</v>
+      </c>
+      <c r="M17">
+        <v>10</v>
+      </c>
+      <c r="N17" s="1">
+        <f t="shared" si="1"/>
+        <v>10.93</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="8">
+        <v>2</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="F18" s="27"/>
+      <c r="K18" s="17">
+        <v>0.29389999999999999</v>
+      </c>
+      <c r="L18" s="79" t="s">
+        <v>232</v>
+      </c>
+      <c r="M18">
+        <v>12</v>
+      </c>
+      <c r="N18" s="1">
+        <f t="shared" si="1"/>
+        <v>3.5267999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
         <v>1</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="23" t="s">
+      <c r="B19" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="49">
+      <c r="C19" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="N19" s="1">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="52">
         <v>1</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="51" t="s">
+      <c r="B20" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>106</v>
-      </c>
-      <c r="F19" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="53"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="58"/>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A20" s="78"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="80"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="84"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="86"/>
-      <c r="M20" t="s">
+      <c r="C20" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="56"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="59"/>
+      <c r="K20" s="60"/>
+      <c r="L20" s="61"/>
+    </row>
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A21" s="80"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
+      <c r="E21" s="82"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="87"/>
+      <c r="L21" s="88"/>
+      <c r="M21" t="s">
+        <v>218</v>
+      </c>
+      <c r="N21" s="1">
+        <f>SUM(N3:N20)</f>
+        <v>61.496720000000003</v>
+      </c>
+      <c r="O21" s="89"/>
+      <c r="P21" s="89"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="89"/>
+      <c r="T21" s="89"/>
+      <c r="U21" s="89"/>
+      <c r="V21" s="89"/>
+      <c r="W21" s="89"/>
+      <c r="X21" s="89"/>
+      <c r="Y21" s="89"/>
+      <c r="Z21" s="89"/>
+      <c r="AA21" s="89"/>
+      <c r="AB21" s="89"/>
+      <c r="AC21" s="89"/>
+    </row>
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>1</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>223</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="17">
+        <v>3.7360000000000002</v>
+      </c>
+      <c r="L22" s="63" t="s">
         <v>225</v>
       </c>
-      <c r="N20" s="1">
-        <f>SUM(N3:N19)</f>
-        <v>47.039920000000002</v>
-      </c>
-      <c r="O20" s="87"/>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="87"/>
-      <c r="W20" s="87"/>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>1</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="F21" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K21" s="13">
-        <v>0</v>
-      </c>
-      <c r="L21" s="75" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
         <v>2</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="23" t="s">
+      <c r="B23" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K22" s="14">
+      <c r="C23" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="17">
         <v>1.643</v>
       </c>
-      <c r="L22" s="60" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>1</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="11"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="14">
-        <v>2.2789999999999999</v>
-      </c>
-      <c r="L23" s="77" t="s">
-        <v>219</v>
+      <c r="L23" s="63" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
+        <v>1</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="17">
+        <v>2.2789999999999999</v>
+      </c>
+      <c r="L24" s="63" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B24" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="23" t="s">
+      <c r="B25" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="I24" s="12">
+      <c r="C25" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I25" s="15">
         <v>1.65</v>
       </c>
-      <c r="J24" s="72">
+      <c r="J25" s="75">
         <v>3434715</v>
       </c>
-      <c r="K24" s="14">
+      <c r="K25" s="17">
         <v>0</v>
       </c>
-      <c r="L24" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="L25" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A26" s="8">
         <v>1</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="23" t="s">
+      <c r="B26" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="I25" s="12">
+      <c r="C26" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I26" s="15">
         <v>1.64</v>
       </c>
-      <c r="J25" s="72">
+      <c r="J26" s="75">
         <v>3434712</v>
       </c>
-      <c r="K25" s="14">
+      <c r="K26" s="17">
         <v>0</v>
       </c>
-      <c r="L25" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="L26" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="23" t="s">
+      <c r="B27" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D26" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="I26" s="12">
+      <c r="C27" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="20">
+        <v>5.68</v>
+      </c>
+      <c r="H27" s="98" t="s">
+        <v>241</v>
+      </c>
+      <c r="I27" s="15">
         <v>7.17</v>
       </c>
-      <c r="J26" s="72">
+      <c r="J27" s="75">
         <v>2300373</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K27" s="17">
         <v>0</v>
       </c>
-      <c r="L26" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="L27" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="8">
         <v>1</v>
       </c>
-      <c r="B27" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="23" t="s">
+      <c r="B28" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="K27" s="14">
+      <c r="C28" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="K28" s="17">
         <v>8.41</v>
       </c>
-      <c r="L27" s="60" t="s">
+      <c r="L28" s="63" t="s">
         <v>174</v>
       </c>
-      <c r="M27" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="M28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A29" s="8">
         <v>1</v>
       </c>
-      <c r="B28" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="23" t="s">
+      <c r="B29" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>107</v>
-      </c>
-      <c r="F28" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="K28" s="14">
-        <v>2.5779999999999998</v>
-      </c>
-      <c r="L28" s="60" t="s">
-        <v>220</v>
-      </c>
-      <c r="M28" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="C29" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="K29" s="17">
+        <v>2.5059999999999998</v>
+      </c>
+      <c r="L29" s="63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A30" s="8">
         <v>1</v>
       </c>
-      <c r="B29" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="23" t="s">
+      <c r="B30" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="24" t="s">
+      <c r="C30" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="K30" s="17">
+        <v>9.67</v>
+      </c>
+      <c r="L30" s="63" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A31" s="8">
+        <v>1</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="K31" s="17">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="L31" s="63" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A32" s="8">
+        <v>1</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" s="20">
+        <v>7.7</v>
+      </c>
+      <c r="H32" s="98" t="s">
+        <v>240</v>
+      </c>
+      <c r="I32" s="15">
+        <v>8.82</v>
+      </c>
+      <c r="J32" s="75">
+        <v>2614867</v>
+      </c>
+      <c r="K32" s="17">
+        <v>0</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="8">
+        <v>1</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="G33" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="H33" s="98" t="s">
+        <v>239</v>
+      </c>
+      <c r="I33" s="15">
+        <v>2.52</v>
+      </c>
+      <c r="J33" s="75">
+        <v>4216300</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="8">
+        <v>2</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" s="20">
+        <v>0</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I34" s="15">
+        <v>7.43</v>
+      </c>
+      <c r="J34" s="75">
+        <v>4137104</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="8">
+        <v>1</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="K29" s="14">
-        <v>9.67</v>
-      </c>
-      <c r="L29" s="60" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="K35" s="17">
+        <v>1.0469999999999999</v>
+      </c>
+      <c r="L35" s="63" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="8">
         <v>1</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="K30" s="14">
-        <v>1.4419999999999999</v>
-      </c>
-      <c r="L30" s="60" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" s="7">
+      <c r="B36" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="17">
+        <v>1.45</v>
+      </c>
+      <c r="L36" s="63" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="8">
         <v>1</v>
       </c>
-      <c r="B31" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="12">
-        <v>8.82</v>
-      </c>
-      <c r="J31" s="72">
-        <v>2614867</v>
-      </c>
-      <c r="K31" s="14">
+      <c r="B37" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="20">
         <v>0</v>
       </c>
-      <c r="L31" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="7">
+      <c r="H37" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="I37" s="15">
+        <v>1.5</v>
+      </c>
+      <c r="J37" s="75">
+        <v>2575555</v>
+      </c>
+      <c r="K37" s="17">
+        <v>0</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="8">
         <v>1</v>
       </c>
-      <c r="B32" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="I32" s="12">
-        <v>2.52</v>
-      </c>
-      <c r="J32" s="72">
-        <v>4216300</v>
-      </c>
-      <c r="K32" s="14">
+      <c r="B38" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="20">
+        <v>1.19</v>
+      </c>
+      <c r="H38" s="98" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" s="15">
         <v>0</v>
       </c>
-      <c r="L32" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="7">
-        <v>2</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="G33" s="17">
+      <c r="J38" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="17">
         <v>0</v>
       </c>
-      <c r="H33" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="12">
-        <v>7.43</v>
-      </c>
-      <c r="J33" s="72">
-        <v>4137104</v>
-      </c>
-      <c r="K33" s="14">
-        <v>0</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="7">
+      <c r="L38" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="M38" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="8">
         <v>1</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="K34" s="14">
-        <v>1.0469999999999999</v>
-      </c>
-      <c r="L34" s="60" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="7">
-        <v>1</v>
-      </c>
-      <c r="B35" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F35" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" s="14">
-        <v>1.45</v>
-      </c>
-      <c r="L35" s="60" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="7">
-        <v>1</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="I36" s="12">
-        <v>1.5</v>
-      </c>
-      <c r="J36" s="72">
-        <v>2575555</v>
-      </c>
-      <c r="K36" s="14">
-        <v>0</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="7">
-        <v>1</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="I37" s="12">
-        <v>0</v>
-      </c>
-      <c r="J37" s="34" t="s">
-        <v>134</v>
-      </c>
-      <c r="K37" s="14">
-        <v>0</v>
-      </c>
-      <c r="L37" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="M37" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="7">
-        <v>1</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="23" t="s">
+      <c r="B39" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D38" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="K38" s="14">
+      <c r="C39" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="17">
         <v>7.11</v>
       </c>
-      <c r="L38" s="60" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="24"/>
+      <c r="L39" s="63" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="24"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="24"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="24"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="24"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="24"/>
-      <c r="I44" s="12" cm="1">
-        <f t="array" ref="I44">SUM(I21:I43*A21:A43)</f>
+      <c r="A44" s="8"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="8"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="12" cm="1">
+        <f t="array" ref="G45">SUM(G22:G44*A22:A44)</f>
+        <v>21.95</v>
+      </c>
+      <c r="H45" s="99" t="s">
+        <v>222</v>
+      </c>
+      <c r="I45" s="15" cm="1">
+        <f t="array" ref="I45">SUM(I22:I44*A22:A44)</f>
         <v>46.980000000000004</v>
       </c>
-      <c r="J44" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="K44" s="14" cm="1">
-        <f t="array" ref="K44">SUM(K21:K43*A21:A43)</f>
-        <v>37.271999999999998</v>
-      </c>
-      <c r="L44" s="15" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="24"/>
+      <c r="J45" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="K45" s="17" cm="1">
+        <f t="array" ref="K45">SUM(K22:K44*A22:A44)</f>
+        <v>40.936</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="24"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="2"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="24"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="24"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="27"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="2"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="24"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="27"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="24"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="27"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="7"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="24"/>
+      <c r="A51" s="8"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="27"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="24"/>
+      <c r="A52" s="8"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="27"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="7"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="24"/>
+      <c r="A53" s="8"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="27"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="7"/>
-      <c r="B54" s="22"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="24"/>
+      <c r="A54" s="8"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="27"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="7"/>
-      <c r="B55" s="22"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="24"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="26"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="27"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="7"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="24"/>
+      <c r="A56" s="8"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="27"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="7"/>
-      <c r="B57" s="22"/>
-      <c r="C57" s="23"/>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="24"/>
+      <c r="A57" s="8"/>
+      <c r="B57" s="25"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="27"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
-      <c r="B58" s="22"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="24"/>
+      <c r="A58" s="8"/>
+      <c r="B58" s="25"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="27"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="7"/>
-      <c r="B59" s="22"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="24"/>
+      <c r="A59" s="8"/>
+      <c r="B59" s="25"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="27"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60" s="22"/>
-      <c r="C60" s="23"/>
-      <c r="D60" s="23"/>
-      <c r="E60" s="23"/>
-      <c r="F60" s="24"/>
+      <c r="A60" s="8"/>
+      <c r="B60" s="25"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="27"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="7"/>
-      <c r="B61" s="22"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="24"/>
+      <c r="A61" s="8"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="27"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="8"/>
+      <c r="B62" s="25"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3290,22 +3456,28 @@
     <hyperlink ref="L13" r:id="rId11" tooltip="ERA6AEB1153V; Rezystor: thin film; SMD; 0805; 115kΩ; 125mW; ±0,1%; ERA6AEB" display="https://www.tme.eu/pl/details/era6aeb1153v/rezystory-smd/panasonic-industry-europe-gmbh/" xr:uid="{36E75F8F-3A03-4E74-87DB-53CA2D76579B}"/>
     <hyperlink ref="L14" r:id="rId12" tooltip="SMD0805-22K1-1%; Rezystor: thick film; SMD; 0805; 22,1kΩ; 0,125W; ±1%; 150V" display="https://www.tme.eu/pl/details/smd0805-22k1-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f2212t5e/" xr:uid="{F0C989FC-4ECE-4541-A05E-6A4BC7A972E2}"/>
     <hyperlink ref="L15" r:id="rId13" tooltip="SMD0805-15.8K-1%; Rezystor: thick film; SMD; 0805; 15,8kΩ; 0,125W; ±1%; 150V" display="https://www.tme.eu/pl/details/smd0805-15.8k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f1582t5e/" xr:uid="{7C4C7510-0083-4D0F-865E-4EAEF0503E23}"/>
-    <hyperlink ref="L27" r:id="rId14" tooltip="MX-503398-1892; Złącze: do kart; microSD; push-push; SMT; złocony; PIN: 8" display="https://www.tme.eu/pl/details/mx-503398-1892/zlacza-do-kart/molex-interconnect-gmbh/503398-1892/" xr:uid="{41CA23C9-5E45-4B42-A43F-DB5DD1D98173}"/>
-    <hyperlink ref="L28" r:id="rId15" tooltip="UBC-RA-TF; Złącze: USB C; gniazdo; na PCB; SMT; PIN: 12; kątowe 90°; USB 2.0" display="https://www.tme.eu/pl/details/ubc-ra-tf/zlacza-usb-i-ieee1394/jst-j-s-t-deutschland-gmbh/ubc-ra-tf-hf/" xr:uid="{22175DF5-CFC0-413A-AA9E-4087D8031364}"/>
-    <hyperlink ref="L29" r:id="rId16" tooltip="MX-48393-0003; Złącze: USB A; gniazdo; na PCB; THT; PIN: 9; kątowe 90°; USB 3.0" display="https://www.tme.eu/pl/details/mx-48393-0003/zlacza-usb-i-ieee1394/molex-interconnect-gmbh/48393-0003/" xr:uid="{161B6C06-7D9A-45B4-BF83-73704FC9DED8}"/>
-    <hyperlink ref="L30" r:id="rId17" tooltip="SM04B-SRSS-TB; Złącze: przewód-płytka; gniazdo; męskie; 1A; 50V; PIN: 4; SMT; 1mm" display="https://www.tme.eu/pl/details/sm04b-srss-tb/zlacza-sygnalowe-raster-1-00mm/jst-j-s-t-deutschland-gmbh/sm04b-srss-tb-lf-sn/" xr:uid="{3D8DF4B1-A5E0-4057-8DF8-11559C4C671D}"/>
-    <hyperlink ref="L34" r:id="rId18" tooltip="KMR221GLFS; Mikroprzełącznik TACT; SPST-NO; Poz: 2; 0,05A/32VDC; SMT; brak; 2N" display="https://www.tme.eu/pl/details/kmr221glfs/mikroprzelaczniki-tact/c-k-components-sas/kmr221g-lfs/" xr:uid="{EAA54C82-4C4B-4288-905D-0922D34023A7}"/>
-    <hyperlink ref="L35" r:id="rId19" tooltip="AP22653W6-7; IC: power switch; high-side,USB switch; 2,1A; Ch: 1; P-Channel; SMD" display="https://www.tme.eu/pl/details/ap22653w6-7/power-switches-uklady-scalone/diodes-incorporated/" xr:uid="{FF8D462A-C868-44BB-B1D5-1A366A87E4F5}"/>
-    <hyperlink ref="L38" r:id="rId20" tooltip="AP64501SP-13; PMIC; przetwornica DC/DC; Uwej: 3,8÷40VDC; Uwyj: 0,8÷39VDC; 5A" display="https://www.tme.eu/pl/details/ap64501sp-13/regulatory-napiecia-uklady-dc-dc/diodes-incorporated/" xr:uid="{10A6E3B6-37C2-44D7-AFE5-8AFBEA13385A}"/>
-    <hyperlink ref="J24" r:id="rId21" display="https://pl.farnell.com/rohm/sml-a12u8tt86/led-red-63mcd-620nm/dp/3434715" xr:uid="{A970F2E6-E1F2-4E0F-98EA-FA206F9EAFCF}"/>
-    <hyperlink ref="J25" r:id="rId22" display="https://pl.farnell.com/rohm/sml-a12m8tt86/led-yellow-green-25mcd-572nm/dp/3434712" xr:uid="{7802DEB3-204E-4ABA-961C-4F6A1132A234}"/>
-    <hyperlink ref="J26" r:id="rId23" display="https://pl.farnell.com/hirose-hrs/fh12-22s-1sh-55/connector-fpc-ffc-smt-1mm-22way/dp/2300373" xr:uid="{2E5F5143-20FC-4EDA-AB34-37D1813E1E25}"/>
-    <hyperlink ref="J31" r:id="rId24" display="https://pl.farnell.com/molex/46765-1301/hdmi-connector-rcpt-19pos-smt/dp/2614867" xr:uid="{AA8128CA-C977-4D15-B623-590B9BFA43EF}"/>
-    <hyperlink ref="J32" r:id="rId25" display="https://pl.farnell.com/bourns/srn8040ha-3r6m/power-inductor-3-6uh-semishielded/dp/4216300" xr:uid="{7B881564-C6BD-4CCD-A913-C9153C4C340D}"/>
-    <hyperlink ref="J33" r:id="rId26" display="https://pl.farnell.com/amphenol-communications-solutions/10164227-1001a1rlf/mezzanine-conn-rcpt-100pos-2row/dp/4137104" xr:uid="{73121110-59FA-434A-8294-90F79030B990}"/>
-    <hyperlink ref="J36" r:id="rId27" display="https://pl.farnell.com/richtek/rt9742sngv/uswi00154-rt9742sngv/dp/2575555" xr:uid="{746A18AA-1BD9-473D-9F8E-CD14E6D67E1E}"/>
-    <hyperlink ref="L22" r:id="rId28" tooltip="TAJB226K016R; Kondensator: tantalowy; 22uF; 16VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb226k016r/kondensatory-tantalowe-smd/kyocera-avx/tajb226k016rnj/" xr:uid="{BFB3CDCE-FB8D-439E-889C-E25F481A5F25}"/>
-    <hyperlink ref="L23" r:id="rId29" tooltip="TAJD106K035R; Kondensator: tantalowy; 10uF; 35VDC; SMD; D; 2917; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajd106k035r/kondensatory-tantalowe-smd/kyocera-avx/tajd106k035rnj/" xr:uid="{EBEDD7EE-3AC1-4E25-B6D1-C8C39A8169D6}"/>
+    <hyperlink ref="L28" r:id="rId14" tooltip="MX-503398-1892; Złącze: do kart; microSD; push-push; SMT; złocony; PIN: 8" display="https://www.tme.eu/pl/details/mx-503398-1892/zlacza-do-kart/molex-interconnect-gmbh/503398-1892/" xr:uid="{41CA23C9-5E45-4B42-A43F-DB5DD1D98173}"/>
+    <hyperlink ref="L30" r:id="rId15" tooltip="MX-48393-0003; Złącze: USB A; gniazdo; na PCB; THT; PIN: 9; kątowe 90°; USB 3.0" display="https://www.tme.eu/pl/details/mx-48393-0003/zlacza-usb-i-ieee1394/molex-interconnect-gmbh/48393-0003/" xr:uid="{161B6C06-7D9A-45B4-BF83-73704FC9DED8}"/>
+    <hyperlink ref="L31" r:id="rId16" tooltip="SM04B-SRSS-TB; Złącze: przewód-płytka; gniazdo; męskie; 1A; 50V; PIN: 4; SMT; 1mm" display="https://www.tme.eu/pl/details/sm04b-srss-tb/zlacza-sygnalowe-raster-1-00mm/jst-j-s-t-deutschland-gmbh/sm04b-srss-tb-lf-sn/" xr:uid="{3D8DF4B1-A5E0-4057-8DF8-11559C4C671D}"/>
+    <hyperlink ref="L35" r:id="rId17" tooltip="KMR221GLFS; Mikroprzełącznik TACT; SPST-NO; Poz: 2; 0,05A/32VDC; SMT; brak; 2N" display="https://www.tme.eu/pl/details/kmr221glfs/mikroprzelaczniki-tact/c-k-components-sas/kmr221g-lfs/" xr:uid="{EAA54C82-4C4B-4288-905D-0922D34023A7}"/>
+    <hyperlink ref="L36" r:id="rId18" tooltip="AP22653W6-7; IC: power switch; high-side,USB switch; 2,1A; Ch: 1; P-Channel; SMD" display="https://www.tme.eu/pl/details/ap22653w6-7/power-switches-uklady-scalone/diodes-incorporated/" xr:uid="{FF8D462A-C868-44BB-B1D5-1A366A87E4F5}"/>
+    <hyperlink ref="L39" r:id="rId19" tooltip="AP64501SP-13; PMIC; przetwornica DC/DC; Uwej: 3,8÷40VDC; Uwyj: 0,8÷39VDC; 5A" display="https://www.tme.eu/pl/details/ap64501sp-13/regulatory-napiecia-uklady-dc-dc/diodes-incorporated/" xr:uid="{10A6E3B6-37C2-44D7-AFE5-8AFBEA13385A}"/>
+    <hyperlink ref="J25" r:id="rId20" display="https://pl.farnell.com/rohm/sml-a12u8tt86/led-red-63mcd-620nm/dp/3434715" xr:uid="{A970F2E6-E1F2-4E0F-98EA-FA206F9EAFCF}"/>
+    <hyperlink ref="J26" r:id="rId21" display="https://pl.farnell.com/rohm/sml-a12m8tt86/led-yellow-green-25mcd-572nm/dp/3434712" xr:uid="{7802DEB3-204E-4ABA-961C-4F6A1132A234}"/>
+    <hyperlink ref="J27" r:id="rId22" display="https://pl.farnell.com/hirose-hrs/fh12-22s-1sh-55/connector-fpc-ffc-smt-1mm-22way/dp/2300373" xr:uid="{2E5F5143-20FC-4EDA-AB34-37D1813E1E25}"/>
+    <hyperlink ref="J32" r:id="rId23" display="https://pl.farnell.com/molex/46765-1301/hdmi-connector-rcpt-19pos-smt/dp/2614867" xr:uid="{AA8128CA-C977-4D15-B623-590B9BFA43EF}"/>
+    <hyperlink ref="J33" r:id="rId24" display="https://pl.farnell.com/bourns/srn8040ha-3r6m/power-inductor-3-6uh-semishielded/dp/4216300" xr:uid="{7B881564-C6BD-4CCD-A913-C9153C4C340D}"/>
+    <hyperlink ref="J34" r:id="rId25" display="https://pl.farnell.com/amphenol-communications-solutions/10164227-1001a1rlf/mezzanine-conn-rcpt-100pos-2row/dp/4137104" xr:uid="{73121110-59FA-434A-8294-90F79030B990}"/>
+    <hyperlink ref="J37" r:id="rId26" display="https://pl.farnell.com/richtek/rt9742sngv/uswi00154-rt9742sngv/dp/2575555" xr:uid="{746A18AA-1BD9-473D-9F8E-CD14E6D67E1E}"/>
+    <hyperlink ref="L23" r:id="rId27" tooltip="TAJB226K016R; Kondensator: tantalowy; 22uF; 16VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb226k016r/kondensatory-tantalowe-smd/kyocera-avx/tajb226k016rnj/" xr:uid="{BFB3CDCE-FB8D-439E-889C-E25F481A5F25}"/>
+    <hyperlink ref="L24" r:id="rId28" tooltip="TAJD106K035R; Kondensator: tantalowy; 10uF; 35VDC; SMD; D; 2917; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajd106k035r/kondensatory-tantalowe-smd/kyocera-avx/tajd106k035rnj/" xr:uid="{EBEDD7EE-3AC1-4E25-B6D1-C8C39A8169D6}"/>
+    <hyperlink ref="L22" r:id="rId29" tooltip="TAJC106K035R; Kondensator: tantalowy; 10uF; 35VDC; SMD; C; 2312; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajc106k035r/kondensatory-tantalowe-smd/kyocera-avx/tajc106k035rnj/" xr:uid="{D12A82B9-B504-47BD-970E-CB9A33596A1F}"/>
+    <hyperlink ref="L29" r:id="rId30" tooltip="USB4105-GF-A-060; Złącze: USB C; gniazdo; SMT; PIN: 16; pozioma; top board mount; 5A" display="https://www.tme.eu/pl/details/usb4105-gf-a-060/zlacza-usb-i-ieee1394/gct/" xr:uid="{C2863D6E-F34C-4C0F-A08C-B8F9C53E4CE4}"/>
+    <hyperlink ref="L17" r:id="rId31" tooltip="ZL303-2X40P; Złącze: kołkowe; listwa kołkowa; męskie; PIN: 80; THT; proste; 2mm" display="https://www.tme.eu/pl/details/zl303-2x40p/listwy-i-gniazda-kolkowe/connfly/ds1025-05-2x40p8bv1-b/" xr:uid="{740D48C3-340C-4E38-A3F2-F7D2BCD4DDE8}"/>
+    <hyperlink ref="H38" r:id="rId32" xr:uid="{D78F53E7-C810-432B-90F6-50B4EFA47F8A}"/>
+    <hyperlink ref="H33" r:id="rId33" xr:uid="{4506F438-F78B-4807-9DB8-B96491D639F1}"/>
+    <hyperlink ref="H32" r:id="rId34" xr:uid="{0DD2681C-B852-43A0-93A8-1BDA7C1A7B80}"/>
+    <hyperlink ref="H27" r:id="rId35" xr:uid="{F1C61B49-A252-441F-99F2-4E76A87558F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3316,130 +3488,130 @@
   <dimension ref="A1:Y50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="14" style="25" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" style="25" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="25" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="17" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" style="26" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="34" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="14" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="14" style="28" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" style="28" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="21" style="29" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="15" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="37" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="17" customWidth="1"/>
+    <col min="12" max="12" width="30.140625" style="18" customWidth="1"/>
     <col min="13" max="13" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="34"/>
+      <c r="K1" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="39"/>
+    </row>
+    <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="77"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="H2" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="27"/>
-      <c r="I1" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="J1" s="31"/>
-      <c r="K1" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="L1" s="36"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="37" t="s">
-        <v>120</v>
-      </c>
-      <c r="H2" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="K2" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="L2" s="69" t="s">
-        <v>130</v>
+      <c r="I2" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="K2" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="L2" s="72" t="s">
+        <v>131</v>
       </c>
       <c r="M2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="42">
         <v>1</v>
       </c>
-      <c r="B3" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="41" t="s">
+      <c r="B3" s="43" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="48"/>
+      <c r="C3" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="51"/>
       <c r="N3" s="1">
         <f>M3*K3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>134</v>
+      <c r="B4" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>135</v>
       </c>
       <c r="N4" s="1">
         <f t="shared" ref="N4:N9" si="0">M4*K4</f>
@@ -3447,32 +3619,32 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="28"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="14">
+      <c r="B5" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="31"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="17">
         <v>0.2472</v>
       </c>
-      <c r="L5" s="60" t="s">
-        <v>198</v>
+      <c r="L5" s="63" t="s">
+        <v>195</v>
       </c>
       <c r="M5">
         <v>50</v>
@@ -3483,29 +3655,29 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="8">
         <v>10</v>
       </c>
-      <c r="B6" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K6" s="14">
+      <c r="B6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="17">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L6" s="60" t="s">
-        <v>208</v>
+      <c r="L6" s="63" t="s">
+        <v>205</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3516,29 +3688,29 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="8">
         <v>1</v>
       </c>
-      <c r="B7" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K7" s="14">
+      <c r="B7" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="17">
         <v>5.6160000000000002E-2</v>
       </c>
-      <c r="L7" s="60" t="s">
-        <v>207</v>
+      <c r="L7" s="63" t="s">
+        <v>204</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3549,29 +3721,29 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="8">
         <v>2</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K8" s="14">
+      <c r="B8" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="17">
         <v>5.9389999999999998E-2</v>
       </c>
-      <c r="L8" s="60" t="s">
-        <v>206</v>
+      <c r="L8" s="63" t="s">
+        <v>203</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3582,33 +3754,33 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49">
+      <c r="A9" s="52">
         <v>3</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="54"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="57">
+      <c r="B9" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="56"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
+      <c r="K9" s="60">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L9" s="70" t="s">
-        <v>209</v>
+      <c r="L9" s="73" t="s">
+        <v>206</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3619,628 +3791,653 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
-      <c r="B10" s="89"/>
-      <c r="C10" s="90"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="94"/>
-      <c r="K10" s="92"/>
-      <c r="L10" s="95"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="92"/>
+      <c r="E10" s="92"/>
+      <c r="F10" s="93"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="95"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="97"/>
       <c r="M10" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="N10" s="1">
         <f>SUM(N3:N9)</f>
         <v>33.854999999999997</v>
       </c>
-      <c r="O10" s="87"/>
-      <c r="P10" s="87"/>
-      <c r="Q10" s="87"/>
-      <c r="R10" s="87"/>
-      <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
-      <c r="U10" s="87"/>
-      <c r="V10" s="87"/>
-      <c r="W10" s="87"/>
-      <c r="X10" s="87"/>
-      <c r="Y10" s="87"/>
+      <c r="O10" s="89"/>
+      <c r="P10" s="89"/>
+      <c r="Q10" s="89"/>
+      <c r="R10" s="89"/>
+      <c r="S10" s="89"/>
+      <c r="T10" s="89"/>
+      <c r="U10" s="89"/>
+      <c r="V10" s="89"/>
+      <c r="W10" s="89"/>
+      <c r="X10" s="89"/>
+      <c r="Y10" s="89"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="7">
         <v>2</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="13">
+      <c r="B11" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="16">
         <v>1.681</v>
       </c>
-      <c r="L11" s="76" t="s">
+      <c r="L11" s="78" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="8">
+        <v>2</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="D12" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="17">
+        <v>1.478</v>
+      </c>
+      <c r="L12" s="63" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="7">
         <v>2</v>
       </c>
-      <c r="B12" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K12" s="14">
-        <v>1.478</v>
-      </c>
-      <c r="L12" s="60" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="B13" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="17">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="L13" s="63" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="8">
         <v>2</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="14">
-        <v>0.98399999999999999</v>
-      </c>
-      <c r="L13" s="60" t="s">
+      <c r="B14" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0.14940000000000001</v>
+      </c>
+      <c r="L14" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="M14" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15" s="8">
+        <v>1</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" s="17">
+        <v>0.1215</v>
+      </c>
+      <c r="L15" s="63" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="8">
+        <v>1</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="K16" s="17">
+        <v>2.5059999999999998</v>
+      </c>
+      <c r="L16" s="63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="8">
+        <v>1</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="K17" s="17">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="L17" s="63" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="8">
+        <v>1</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="K18" s="17">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="L18" s="63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="8">
+        <v>2</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="K19" s="17">
+        <v>2.25</v>
+      </c>
+      <c r="L19" s="63" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="8">
         <v>2</v>
       </c>
-      <c r="B14" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0.14940000000000001</v>
-      </c>
-      <c r="L14" s="76" t="s">
-        <v>222</v>
-      </c>
-      <c r="M14" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="B20" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="K20" s="17">
+        <v>1.236</v>
+      </c>
+      <c r="L20" s="63" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="8">
+        <v>2</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="27"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="8">
+        <v>3</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="K22" s="17">
+        <v>1.0469999999999999</v>
+      </c>
+      <c r="L22" s="63" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0.1215</v>
-      </c>
-      <c r="L15" s="60" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="B23" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="K23" s="17">
+        <v>23.4</v>
+      </c>
+      <c r="L23" s="63" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F16" s="24"/>
-      <c r="K16" s="14">
-        <v>2.5779999999999998</v>
-      </c>
-      <c r="L16" s="60" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>1</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="K17" s="14">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="L17" s="60" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>1</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="K18" s="14">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="L18" s="60" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>2</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="K19" s="14">
-        <v>2.25</v>
-      </c>
-      <c r="L19" s="60" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>2</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F20" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="K20" s="14">
-        <v>1.236</v>
-      </c>
-      <c r="L20" s="60" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>2</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="24"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>3</v>
-      </c>
-      <c r="B22" s="22" t="s">
-        <v>173</v>
-      </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F22" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="K22" s="14">
-        <v>1.0469999999999999</v>
-      </c>
-      <c r="L22" s="60" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
-        <v>1</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="K23" s="14">
-        <v>23.4</v>
-      </c>
-      <c r="L23" s="60" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>1</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D24" s="23" t="s">
+      <c r="B24" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="D24" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>134</v>
+      <c r="E24" s="23" t="s">
+        <v>135</v>
       </c>
       <c r="F24" t="s">
         <v>172</v>
       </c>
-      <c r="K24" s="14">
+      <c r="G24" s="20">
+        <v>18.75</v>
+      </c>
+      <c r="H24" s="98" t="s">
+        <v>237</v>
+      </c>
+      <c r="K24" s="17">
         <v>0</v>
       </c>
-      <c r="L24" s="15" t="s">
-        <v>134</v>
+      <c r="L24" s="18" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="23" t="s">
+      <c r="B25" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="K25" s="14">
+      <c r="E25" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="17">
         <v>1.5349999999999999</v>
       </c>
-      <c r="L25" s="60" t="s">
-        <v>189</v>
+      <c r="L25" s="63" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="24"/>
+      <c r="A26" s="8">
+        <v>1</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" t="s">
+        <v>242</v>
+      </c>
+      <c r="G26" s="20">
+        <v>3.41</v>
+      </c>
+      <c r="H26" s="98" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="24"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="22"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="24"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7"/>
-      <c r="B29" s="22"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7"/>
-      <c r="B30" s="22"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="24"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7"/>
-      <c r="B31" s="22"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="24"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="24"/>
-      <c r="K32" s="14" cm="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="12" cm="1">
+        <f t="array" ref="G32">SUM(G11:G30*A11:A30)</f>
+        <v>22.16</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K32" s="17" cm="1">
         <f t="array" ref="K32">SUM(K11:K30*A11:A30)</f>
-        <v>49.696300000000001</v>
-      </c>
-      <c r="L32" s="15" t="s">
-        <v>229</v>
+        <v>49.771299999999997</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="24"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7"/>
-      <c r="B34" s="22"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="24"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="27"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="24"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="27"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7"/>
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="24"/>
+      <c r="A36" s="8"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="27"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7"/>
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="24"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="27"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7"/>
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="24"/>
+      <c r="A38" s="8"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="27"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="24"/>
+      <c r="A39" s="8"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="27"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="7"/>
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="24"/>
+      <c r="A40" s="8"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="27"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="7"/>
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="24"/>
+      <c r="A41" s="8"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="27"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="7"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="24"/>
+      <c r="A42" s="8"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="27"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="7"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="24"/>
+      <c r="A43" s="8"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="27"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="24"/>
+      <c r="A44" s="8"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="27"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="7"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="24"/>
+      <c r="A45" s="8"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="7"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="23"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="24"/>
+      <c r="A46" s="8"/>
+      <c r="B46" s="25"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="27"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="7"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="24"/>
+      <c r="A47" s="8"/>
+      <c r="B47" s="25"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="7"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="24"/>
+      <c r="A48" s="8"/>
+      <c r="B48" s="25"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="27"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="7"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="24"/>
+      <c r="A49" s="8"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="27"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="7"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="24"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4263,16 +4460,98 @@
     <hyperlink ref="L13" r:id="rId6" tooltip="MBR1020VL-AU-R1; Dioda: prostownicza Schottky; SOD123F; SMD; 20V; 1A; rolka,taśma" display="https://www.tme.eu/pl/details/mbr1020vl-au-r1/diody-schottky-smd/panjit-semiconductor-panjit-international-inc/mbr1020vl-au-r1-000a1/" xr:uid="{A0047D2D-5F9E-455D-8209-D634D4EE13DD}"/>
     <hyperlink ref="L14" r:id="rId7" tooltip="LTST-C190KRKT; LED; czerwony; SMD; 0603; 18÷180mcd; 1,6÷2,4VDC; 1,6x0,8x0,8mm" display="https://www.tme.eu/pl/details/ltst-c190krkt/diody-led-smd-kolorowe/lite-on-technology/" xr:uid="{323C6E20-A245-4FFF-9A77-3B266CA16295}"/>
     <hyperlink ref="L15" r:id="rId8" tooltip="LTST-C190KGKT; LED; zielony; SMD; 0603; 18÷71mcd; 1,9÷2,4VDC; 1,6x0,8x0,8mm; 130°" display="https://www.tme.eu/pl/details/ltst-c190kgkt/diody-led-smd-kolorowe/lite-on-technology/" xr:uid="{C8E5E74A-2D5E-4713-8DAC-508AA38D50D5}"/>
-    <hyperlink ref="L16" r:id="rId9" tooltip="UBC-RA-TF; Złącze: USB C; gniazdo; na PCB; SMT; PIN: 12; kątowe 90°; USB 2.0" display="https://www.tme.eu/pl/details/ubc-ra-tf/zlacza-usb-i-ieee1394/jst-j-s-t-deutschland-gmbh/ubc-ra-tf-hf/" xr:uid="{87430E5F-AC5E-41B8-A6E0-D593068F170D}"/>
-    <hyperlink ref="L17" r:id="rId10" tooltip="MX-53047-0210; Złącze: przewód-płytka; gniazdo; męskie; PIN: 2; PicoBlade™; proste" display="https://www.tme.eu/pl/details/mx-53047-0210/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53047-0210/" xr:uid="{6268CDE7-AD64-4834-BBAC-08F566CBE9BF}"/>
-    <hyperlink ref="L18" r:id="rId11" tooltip="MX-53048-0210; Złącze: przewód-płytka; gniazdo; męskie; PIN: 2; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0210/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0210/" xr:uid="{2FF8517A-7638-445D-B16A-C54A9C0E30C2}"/>
-    <hyperlink ref="L19" r:id="rId12" tooltip="MX-53048-0810; Złącze: przewód-płytka; gniazdo; męskie; PIN: 8; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0810/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0810/" xr:uid="{73E29112-7FEB-4BB3-81BC-64FBA43E7FD3}"/>
-    <hyperlink ref="L20" r:id="rId13" tooltip="AO3401A; Tranzystor: P-MOSFET; unipolarny; -30V; -4A; 1,4W; SOT23" display="https://www.tme.eu/pl/details/ao3401a/tranzystory-z-kanalem-p-smd/alpha-omega-semiconductor-inc/" xr:uid="{E8F71310-8785-4870-96A1-58C869082172}"/>
-    <hyperlink ref="L22" r:id="rId14" tooltip="KMR221GLFS; Mikroprzełącznik TACT; SPST-NO; Poz: 2; 0,05A/32VDC; SMT; brak; 2N" display="https://www.tme.eu/pl/details/kmr221glfs/mikroprzelaczniki-tact/c-k-components-sas/kmr221g-lfs/" xr:uid="{5CA423C8-A7FC-4735-8747-162D36AE1DDC}"/>
-    <hyperlink ref="L23" r:id="rId15" tooltip="ESP32S3-WRM1U-16R8; Moduł: IoT; Bluetooth: BLE; WiFi; zewnętrzna; IEEE 802.11b/g/n" display="https://www.tme.eu/pl/details/esp32s3-wrm1u-16r8/moduly-iot-wifi-bluetooth/espressif-systems/esp32-s3-wroom-1u-n16r8/" xr:uid="{D9EF05AA-AF83-4597-BDF8-BA137CBB6E85}"/>
-    <hyperlink ref="L25" r:id="rId16" tooltip="AP7361C-33E-13; IC: stabilizator napięcia; LDO,liniowy,nieregulowany; 3,3V; 1A" display="https://www.tme.eu/pl/details/ap7361c-33e-13/stabilizatory-napiecia-nieregulowane-ldo/diodes-incorporated/" xr:uid="{B6837D71-21FA-4114-82ED-638BCE656B89}"/>
-    <hyperlink ref="L11" r:id="rId17" tooltip="TAJB475K035R; Kondensator: tantalowy; 4,7uF; 35VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb475k035r/kondensatory-tantalowe-smd/kyocera-avx/tajb475k035rnj/" xr:uid="{733D9C56-D9FD-40D8-B935-70D7303A755D}"/>
-    <hyperlink ref="L12" r:id="rId18" tooltip="TAJA475K010R; Kondensator: tantalowy; 4,7uF; 10VDC; SMD; A; 1206; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/taja475k010r/kondensatory-tantalowe-smd/kyocera-avx/taja475k010rnj/" xr:uid="{9602A5DC-2927-4916-9728-54DC4152DDB1}"/>
+    <hyperlink ref="L18" r:id="rId9" tooltip="MX-53048-0210; Złącze: przewód-płytka; gniazdo; męskie; PIN: 2; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0210/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0210/" xr:uid="{2FF8517A-7638-445D-B16A-C54A9C0E30C2}"/>
+    <hyperlink ref="L19" r:id="rId10" tooltip="MX-53048-0810; Złącze: przewód-płytka; gniazdo; męskie; PIN: 8; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0810/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0810/" xr:uid="{73E29112-7FEB-4BB3-81BC-64FBA43E7FD3}"/>
+    <hyperlink ref="L20" r:id="rId11" tooltip="AO3401A; Tranzystor: P-MOSFET; unipolarny; -30V; -4A; 1,4W; SOT23" display="https://www.tme.eu/pl/details/ao3401a/tranzystory-z-kanalem-p-smd/alpha-omega-semiconductor-inc/" xr:uid="{E8F71310-8785-4870-96A1-58C869082172}"/>
+    <hyperlink ref="L22" r:id="rId12" tooltip="KMR221GLFS; Mikroprzełącznik TACT; SPST-NO; Poz: 2; 0,05A/32VDC; SMT; brak; 2N" display="https://www.tme.eu/pl/details/kmr221glfs/mikroprzelaczniki-tact/c-k-components-sas/kmr221g-lfs/" xr:uid="{5CA423C8-A7FC-4735-8747-162D36AE1DDC}"/>
+    <hyperlink ref="L23" r:id="rId13" tooltip="ESP32S3-WRM1U-16R8; Moduł: IoT; Bluetooth: BLE; WiFi; zewnętrzna; IEEE 802.11b/g/n" display="https://www.tme.eu/pl/details/esp32s3-wrm1u-16r8/moduly-iot-wifi-bluetooth/espressif-systems/esp32-s3-wroom-1u-n16r8/" xr:uid="{D9EF05AA-AF83-4597-BDF8-BA137CBB6E85}"/>
+    <hyperlink ref="L25" r:id="rId14" tooltip="AP7361C-33E-13; IC: stabilizator napięcia; LDO,liniowy,nieregulowany; 3,3V; 1A" display="https://www.tme.eu/pl/details/ap7361c-33e-13/stabilizatory-napiecia-nieregulowane-ldo/diodes-incorporated/" xr:uid="{B6837D71-21FA-4114-82ED-638BCE656B89}"/>
+    <hyperlink ref="L11" r:id="rId15" tooltip="TAJB475K035R; Kondensator: tantalowy; 4,7uF; 35VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb475k035r/kondensatory-tantalowe-smd/kyocera-avx/tajb475k035rnj/" xr:uid="{733D9C56-D9FD-40D8-B935-70D7303A755D}"/>
+    <hyperlink ref="L12" r:id="rId16" tooltip="TAJA475K010R; Kondensator: tantalowy; 4,7uF; 10VDC; SMD; A; 1206; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/taja475k010r/kondensatory-tantalowe-smd/kyocera-avx/taja475k010rnj/" xr:uid="{9602A5DC-2927-4916-9728-54DC4152DDB1}"/>
+    <hyperlink ref="L16" r:id="rId17" tooltip="USB4105-GF-A-060; Złącze: USB C; gniazdo; SMT; PIN: 16; pozioma; top board mount; 5A" display="https://www.tme.eu/pl/details/usb4105-gf-a-060/zlacza-usb-i-ieee1394/gct/" xr:uid="{E6AF3DF7-54A7-43BB-B68B-CA8D5EC857F5}"/>
+    <hyperlink ref="L17" r:id="rId18" tooltip="MX-53047-0310; Złącze: przewód-płytka; gniazdo; męskie; PIN: 3; PicoBlade™; proste" display="https://www.tme.eu/pl/details/mx-53047-0310/zlacza-sygnalowe-raster-1-25mm/molex/53047-0310/" xr:uid="{6A3C36BE-6AF7-4D8F-8F50-6A60C563C0A2}"/>
+    <hyperlink ref="H24" r:id="rId19" display="Wio-SX1262 " xr:uid="{9CAEFD2C-C782-4CCF-A583-DF19A0BE7BDB}"/>
+    <hyperlink ref="H26" r:id="rId20" xr:uid="{5E024DD1-6DC1-4BB2-A0FD-5999C67AD13E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58753BDD-603F-4060-8AE8-940A823D2E6E}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="100" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="100" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="100" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="100" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="100" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="100" t="s">
+        <v>242</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A5" r:id="rId1" xr:uid="{38454E2E-B1BE-46EF-BFE2-BB210E6FCC6C}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{60FBE8F9-7523-4577-ABCF-99B62829F7C3}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{087AF819-D1CD-4701-A4BC-81281096ACC8}"/>
+    <hyperlink ref="A2" r:id="rId4" xr:uid="{B5F647DA-2F1B-40BE-AD44-317720BD18EC}"/>
+    <hyperlink ref="A6" r:id="rId5" display="Wio-SX1262 " xr:uid="{F42343D2-42D5-40EB-9DBC-B5056D091598}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{66EB5D16-345E-4639-BF59-600DE26B5E94}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F15D77-D0DC-404B-AF29-66E386CE219D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA61079-F0D4-4988-8A58-AF5CA445418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="248">
   <si>
     <t>Ilość</t>
   </si>
@@ -791,10 +791,19 @@
     <t xml:space="preserve">ANTX150P116B08683 </t>
   </si>
   <si>
-    <t>!!!!!!!!!!!!</t>
-  </si>
-  <si>
     <t>Kod</t>
+  </si>
+  <si>
+    <t>DF40C-100DS-0.4V(51) (substitute)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835-RT9742SNGV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">859-LTST-S270KRKT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">859-LTST-S270KGKT </t>
   </si>
 </sst>
 </file>
@@ -802,7 +811,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$zł-415]_-;\-* #,##0.00\ [$zł-415]_-;_-* &quot;-&quot;??\ [$zł-415]_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1482,142 +1491,150 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="35" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="36" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="31" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1956,76 +1973,76 @@
   <dimension ref="A1:AC62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="14" style="28" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="28" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="20" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="29" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="15" customWidth="1"/>
-    <col min="10" max="10" width="30.140625" style="37" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="17" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" style="13" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="101" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="92" customWidth="1"/>
+    <col min="10" max="10" width="30.140625" style="25" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="10" customWidth="1"/>
+    <col min="12" max="12" width="30.140625" style="11" customWidth="1"/>
     <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="98"/>
+      <c r="I1" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="38" t="s">
+      <c r="J1" s="84"/>
+      <c r="K1" s="85" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="39"/>
+      <c r="L1" s="86"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="64"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="67" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="68" t="s">
+      <c r="H2" s="99" t="s">
         <v>131</v>
       </c>
-      <c r="I2" s="69" t="s">
+      <c r="I2" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="J2" s="70" t="s">
+      <c r="J2" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="71" t="s">
+      <c r="K2" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="L2" s="53" t="s">
         <v>131</v>
       </c>
       <c r="M2" t="s">
@@ -2033,32 +2050,32 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="42">
+      <c r="A3" s="28">
         <v>4</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="50">
+      <c r="F3" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="36">
         <v>3.9190000000000003E-2</v>
       </c>
-      <c r="L3" s="74" t="s">
+      <c r="L3" s="55" t="s">
         <v>196</v>
       </c>
       <c r="M3">
@@ -2070,28 +2087,28 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K4" s="17">
+      <c r="E4" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K4" s="10">
         <v>0.20480000000000001</v>
       </c>
-      <c r="L4" s="63" t="s">
+      <c r="L4" s="49" t="s">
         <v>191</v>
       </c>
       <c r="M4">
@@ -2103,28 +2120,28 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="3">
         <v>1</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K5" s="17">
+      <c r="E5" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K5" s="10">
         <v>0.18210000000000001</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="49" t="s">
         <v>190</v>
       </c>
       <c r="M5">
@@ -2136,28 +2153,28 @@
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="3">
         <v>1</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K6" s="17">
+      <c r="E6" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="10">
         <v>0.1421</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="49" t="s">
         <v>192</v>
       </c>
       <c r="M6">
@@ -2169,28 +2186,28 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K7" s="17">
+      <c r="E7" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="10">
         <v>4.1669999999999999E-2</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="49" t="s">
         <v>193</v>
       </c>
       <c r="M7">
@@ -2202,28 +2219,28 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="3">
         <v>4</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K8" s="17">
+      <c r="F8" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="10">
         <v>0.28220000000000001</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="49" t="s">
         <v>194</v>
       </c>
       <c r="M8">
@@ -2235,28 +2252,28 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="3">
         <v>3</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F9" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K9" s="17">
+      <c r="F9" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K9" s="10">
         <v>3.3119999999999997E-2</v>
       </c>
-      <c r="L9" s="63" t="s">
+      <c r="L9" s="49" t="s">
         <v>199</v>
       </c>
       <c r="M9">
@@ -2268,28 +2285,28 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="3">
         <v>4</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K10" s="17">
+      <c r="F10" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="10">
         <v>3.9050000000000001E-2</v>
       </c>
-      <c r="L10" s="63" t="s">
+      <c r="L10" s="49" t="s">
         <v>200</v>
       </c>
       <c r="M10">
@@ -2301,28 +2318,28 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="3">
         <v>2</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K11" s="17">
+      <c r="F11" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K11" s="10">
         <v>1.7569999999999999E-2</v>
       </c>
-      <c r="L11" s="63" t="s">
+      <c r="L11" s="49" t="s">
         <v>201</v>
       </c>
       <c r="M11">
@@ -2334,28 +2351,28 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="3">
         <v>1</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="17">
+      <c r="F12" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="10">
         <v>3.6560000000000002E-2</v>
       </c>
-      <c r="L12" s="63" t="s">
+      <c r="L12" s="49" t="s">
         <v>202</v>
       </c>
       <c r="M12">
@@ -2367,28 +2384,28 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="3">
         <v>1</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E13" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K13" s="17">
+      <c r="E13" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K13" s="10">
         <v>0.21560000000000001</v>
       </c>
-      <c r="L13" s="63" t="s">
+      <c r="L13" s="49" t="s">
         <v>189</v>
       </c>
       <c r="M13">
@@ -2400,28 +2417,28 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="3">
         <v>1</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K14" s="17">
+      <c r="E14" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K14" s="10">
         <v>5.9389999999999998E-2</v>
       </c>
-      <c r="L14" s="63" t="s">
+      <c r="L14" s="49" t="s">
         <v>198</v>
       </c>
       <c r="M14">
@@ -2433,28 +2450,28 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="3">
         <v>1</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="17">
+      <c r="E15" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K15" s="10">
         <v>6.7129999999999995E-2</v>
       </c>
-      <c r="L15" s="63" t="s">
+      <c r="L15" s="49" t="s">
         <v>197</v>
       </c>
       <c r="M15">
@@ -2466,25 +2483,25 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="L16" s="18" t="s">
+      <c r="E16" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="L16" s="11" t="s">
         <v>229</v>
       </c>
       <c r="M16" s="1"/>
@@ -2494,28 +2511,28 @@
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="3">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="E17" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="F17" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K17" s="17">
+      <c r="F17" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K17" s="10">
         <v>1.093</v>
       </c>
-      <c r="L17" s="79" t="s">
+      <c r="L17" s="58" t="s">
         <v>230</v>
       </c>
       <c r="M17">
@@ -2527,22 +2544,22 @@
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="3">
         <v>2</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="K18" s="17">
+      <c r="F18" s="19"/>
+      <c r="K18" s="10">
         <v>0.29389999999999999</v>
       </c>
-      <c r="L18" s="79" t="s">
+      <c r="L18" s="58" t="s">
         <v>232</v>
       </c>
       <c r="M18">
@@ -2554,22 +2571,22 @@
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="A19" s="3">
         <v>1</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E19" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>135</v>
       </c>
       <c r="N19" s="1">
@@ -2578,44 +2595,44 @@
       </c>
     </row>
     <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="52">
+      <c r="A20" s="38">
         <v>1</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="54" t="s">
+      <c r="C20" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="54" t="s">
+      <c r="D20" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="54" t="s">
+      <c r="E20" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="F20" s="55" t="s">
+      <c r="F20" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="56"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="60"/>
-      <c r="L20" s="61"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="95"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="80"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
-      <c r="E21" s="82"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="84"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="84"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="87"/>
-      <c r="L21" s="88"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="60"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="62"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="65"/>
       <c r="M21" t="s">
         <v>218</v>
       </c>
@@ -2623,241 +2640,241 @@
         <f>SUM(N3:N20)</f>
         <v>61.496720000000003</v>
       </c>
-      <c r="O21" s="89"/>
-      <c r="P21" s="89"/>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="89"/>
-      <c r="T21" s="89"/>
-      <c r="U21" s="89"/>
-      <c r="V21" s="89"/>
-      <c r="W21" s="89"/>
-      <c r="X21" s="89"/>
-      <c r="Y21" s="89"/>
-      <c r="Z21" s="89"/>
-      <c r="AA21" s="89"/>
-      <c r="AB21" s="89"/>
-      <c r="AC21" s="89"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="66"/>
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+      <c r="W21" s="66"/>
+      <c r="X21" s="66"/>
+      <c r="Y21" s="66"/>
+      <c r="Z21" s="66"/>
+      <c r="AA21" s="66"/>
+      <c r="AB21" s="66"/>
+      <c r="AC21" s="66"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="3">
         <v>1</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="18" t="s">
         <v>224</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="E22" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F22" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K22" s="17">
+      <c r="F22" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K22" s="10">
         <v>3.7360000000000002</v>
       </c>
-      <c r="L22" s="63" t="s">
+      <c r="L22" s="49" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="3">
         <v>2</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="E23" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F23" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K23" s="17">
+      <c r="F23" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K23" s="10">
         <v>1.643</v>
       </c>
-      <c r="L23" s="63" t="s">
+      <c r="L23" s="49" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="2">
         <v>1</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="F24" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="17">
+      <c r="F24" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G24" s="12"/>
+      <c r="H24" s="104"/>
+      <c r="I24" s="97"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="10">
         <v>2.2789999999999999</v>
       </c>
-      <c r="L24" s="63" t="s">
+      <c r="L24" s="49" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="A25" s="3">
         <v>2</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="E25" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="27" t="s">
+      <c r="F25" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="13">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="H25" s="105" t="s">
+        <v>246</v>
+      </c>
+      <c r="I25" s="92">
+        <v>1.65</v>
+      </c>
+      <c r="J25" s="56">
+        <v>3434715</v>
+      </c>
+      <c r="K25" s="10">
         <v>0</v>
       </c>
-      <c r="H25" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I25" s="15">
-        <v>1.65</v>
-      </c>
-      <c r="J25" s="75">
-        <v>3434715</v>
-      </c>
-      <c r="K25" s="17">
+      <c r="L25" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>1</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="13">
+        <v>0.30499999999999999</v>
+      </c>
+      <c r="H26" s="105" t="s">
+        <v>247</v>
+      </c>
+      <c r="I26" s="92">
+        <v>1.64</v>
+      </c>
+      <c r="J26" s="56">
+        <v>3434712</v>
+      </c>
+      <c r="K26" s="10">
         <v>0</v>
       </c>
-      <c r="L25" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="L26" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>2</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="G27" s="13">
+        <v>5.68</v>
+      </c>
+      <c r="H27" s="105" t="s">
+        <v>241</v>
+      </c>
+      <c r="I27" s="92">
+        <v>7.17</v>
+      </c>
+      <c r="J27" s="56">
+        <v>2300373</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>1</v>
       </c>
-      <c r="B26" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="G26" s="20">
-        <v>0</v>
-      </c>
-      <c r="H26" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I26" s="15">
-        <v>1.64</v>
-      </c>
-      <c r="J26" s="75">
-        <v>3434712</v>
-      </c>
-      <c r="K26" s="17">
-        <v>0</v>
-      </c>
-      <c r="L26" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
-        <v>2</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="G27" s="20">
-        <v>5.68</v>
-      </c>
-      <c r="H27" s="98" t="s">
-        <v>241</v>
-      </c>
-      <c r="I27" s="15">
-        <v>7.17</v>
-      </c>
-      <c r="J27" s="75">
-        <v>2300373</v>
-      </c>
-      <c r="K27" s="17">
-        <v>0</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
-        <v>1</v>
-      </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="E28" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="10">
         <v>8.41</v>
       </c>
-      <c r="L28" s="63" t="s">
+      <c r="L28" s="49" t="s">
         <v>174</v>
       </c>
       <c r="M28" t="s">
@@ -2865,322 +2882,322 @@
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+      <c r="A29" s="3">
         <v>1</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="E29" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="K29" s="17">
+      <c r="K29" s="10">
         <v>2.5059999999999998</v>
       </c>
-      <c r="L29" s="63" t="s">
+      <c r="L29" s="49" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
+      <c r="A30" s="3">
         <v>1</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="K30" s="17">
+      <c r="K30" s="10">
         <v>9.67</v>
       </c>
-      <c r="L30" s="63" t="s">
+      <c r="L30" s="49" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
+      <c r="A31" s="3">
         <v>1</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="26" t="s">
+      <c r="E31" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="K31" s="17">
+      <c r="K31" s="10">
         <v>1.4419999999999999</v>
       </c>
-      <c r="L31" s="63" t="s">
+      <c r="L31" s="49" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
+      <c r="A32" s="3">
         <v>1</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="26" t="s">
+      <c r="E32" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="13">
         <v>7.7</v>
       </c>
-      <c r="H32" s="98" t="s">
+      <c r="H32" s="105" t="s">
         <v>240</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="92">
         <v>8.82</v>
       </c>
-      <c r="J32" s="75">
+      <c r="J32" s="56">
         <v>2614867</v>
       </c>
-      <c r="K32" s="17">
+      <c r="K32" s="10">
         <v>0</v>
       </c>
-      <c r="L32" s="18" t="s">
+      <c r="L32" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+      <c r="A33" s="3">
         <v>1</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F33" s="27" t="s">
+      <c r="E33" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="13">
         <v>1.7</v>
       </c>
-      <c r="H33" s="98" t="s">
+      <c r="H33" s="105" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I33" s="92">
         <v>2.52</v>
       </c>
-      <c r="J33" s="75">
+      <c r="J33" s="56">
         <v>4216300</v>
       </c>
-      <c r="K33" s="17">
+      <c r="K33" s="10">
         <v>0</v>
       </c>
-      <c r="L33" s="18" t="s">
+      <c r="L33" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+      <c r="A34" s="3">
         <v>2</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="26" t="s">
+      <c r="D34" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="13">
+        <v>5.5529999999999999</v>
+      </c>
+      <c r="H34" s="105" t="s">
+        <v>244</v>
+      </c>
+      <c r="I34" s="92">
+        <v>7.43</v>
+      </c>
+      <c r="J34" s="56">
+        <v>4137104</v>
+      </c>
+      <c r="K34" s="10">
         <v>0</v>
       </c>
-      <c r="H34" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I34" s="15">
-        <v>7.43</v>
-      </c>
-      <c r="J34" s="75">
-        <v>4137104</v>
-      </c>
-      <c r="K34" s="17">
+      <c r="L34" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
+        <v>1</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="10">
+        <v>1.0469999999999999</v>
+      </c>
+      <c r="L35" s="49" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <v>1</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="10">
+        <v>1.45</v>
+      </c>
+      <c r="L36" s="49" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
+        <v>1</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="13">
+        <v>1.04</v>
+      </c>
+      <c r="H37" s="105" t="s">
+        <v>245</v>
+      </c>
+      <c r="I37" s="92">
+        <v>1.5</v>
+      </c>
+      <c r="J37" s="56">
+        <v>2575555</v>
+      </c>
+      <c r="K37" s="10">
         <v>0</v>
       </c>
-      <c r="L34" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
+      <c r="L37" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>1</v>
       </c>
-      <c r="B35" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="K35" s="17">
-        <v>1.0469999999999999</v>
-      </c>
-      <c r="L35" s="63" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
-        <v>1</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="F36" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="K36" s="17">
-        <v>1.45</v>
-      </c>
-      <c r="L36" s="63" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
-        <v>1</v>
-      </c>
-      <c r="B37" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C37" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="G37" s="20">
+      <c r="B38" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="G38" s="13">
+        <v>1.19</v>
+      </c>
+      <c r="H38" s="105" t="s">
+        <v>238</v>
+      </c>
+      <c r="I38" s="92">
         <v>0</v>
       </c>
-      <c r="H37" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="I37" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="J37" s="75">
-        <v>2575555</v>
-      </c>
-      <c r="K37" s="17">
+      <c r="J38" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="10">
         <v>0</v>
       </c>
-      <c r="L37" s="18" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
-        <v>1</v>
-      </c>
-      <c r="B38" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="G38" s="20">
-        <v>1.19</v>
-      </c>
-      <c r="H38" s="98" t="s">
-        <v>238</v>
-      </c>
-      <c r="I38" s="15">
-        <v>0</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="K38" s="17">
-        <v>0</v>
-      </c>
-      <c r="L38" s="18" t="s">
+      <c r="L38" s="11" t="s">
         <v>135</v>
       </c>
       <c r="M38" t="s">
@@ -3188,259 +3205,259 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="A39" s="3">
         <v>1</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="E39" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="F39" s="27" t="s">
+      <c r="E39" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="K39" s="17">
+      <c r="K39" s="10">
         <v>7.11</v>
       </c>
-      <c r="L39" s="63" t="s">
+      <c r="L39" s="49" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="27"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="19"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="27"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="2"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="2"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="2"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="12" cm="1">
+      <c r="A45" s="3"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="5" cm="1">
         <f t="array" ref="G45">SUM(G22:G44*A22:A44)</f>
-        <v>21.95</v>
-      </c>
-      <c r="H45" s="99" t="s">
+        <v>35.166999999999994</v>
+      </c>
+      <c r="H45" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I45" s="15" cm="1">
+      <c r="I45" s="92" cm="1">
         <f t="array" ref="I45">SUM(I22:I44*A22:A44)</f>
         <v>46.980000000000004</v>
       </c>
-      <c r="J45" s="37" t="s">
+      <c r="J45" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="K45" s="17" cm="1">
+      <c r="K45" s="10" cm="1">
         <f t="array" ref="K45">SUM(K22:K44*A22:A44)</f>
         <v>40.936</v>
       </c>
-      <c r="L45" s="18" t="s">
+      <c r="L45" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="2"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="2"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="2"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="27"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="19"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="27"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="25"/>
-      <c r="C51" s="26"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="27"/>
+      <c r="A51" s="3"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="19"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="26"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="27"/>
+      <c r="A52" s="3"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="19"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="27"/>
+      <c r="A53" s="3"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="19"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="25"/>
-      <c r="C54" s="26"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="26"/>
-      <c r="F54" s="27"/>
+      <c r="A54" s="3"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="19"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="26"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="26"/>
-      <c r="F55" s="27"/>
+      <c r="A55" s="3"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="19"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="27"/>
+      <c r="A56" s="3"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="19"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="26"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="26"/>
-      <c r="F57" s="27"/>
+      <c r="A57" s="3"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="19"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="8"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="26"/>
-      <c r="F58" s="27"/>
+      <c r="A58" s="3"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="19"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="8"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="26"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="26"/>
-      <c r="F59" s="27"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="19"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="8"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="26"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="26"/>
-      <c r="F60" s="27"/>
+      <c r="A60" s="3"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="19"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="8"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="26"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="26"/>
-      <c r="F61" s="27"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="19"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="8"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="26"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="26"/>
-      <c r="F62" s="27"/>
+      <c r="A62" s="3"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" tooltip="04025C104KAT2A; Kondensator: ceramiczny; MLCC; 100nF; 50V; X7R; ±10%; SMD; 0402" display="https://www.tme.eu/pl/details/04025c104kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{4885974C-EAC2-4390-9084-66DCF3F94398}"/>
@@ -3478,6 +3495,10 @@
     <hyperlink ref="H33" r:id="rId33" xr:uid="{4506F438-F78B-4807-9DB8-B96491D639F1}"/>
     <hyperlink ref="H32" r:id="rId34" xr:uid="{0DD2681C-B852-43A0-93A8-1BDA7C1A7B80}"/>
     <hyperlink ref="H27" r:id="rId35" xr:uid="{F1C61B49-A252-441F-99F2-4E76A87558F1}"/>
+    <hyperlink ref="H34" r:id="rId36" display="DF40C-100DS-0.4V(51)" xr:uid="{236B2014-34E9-4339-94F8-870F059483AE}"/>
+    <hyperlink ref="H37" r:id="rId37" xr:uid="{D38265A8-7155-483A-A751-D36348DE3503}"/>
+    <hyperlink ref="H25" r:id="rId38" xr:uid="{648F9DD1-59B7-454C-A8BD-19F2BA8224D4}"/>
+    <hyperlink ref="H26" r:id="rId39" xr:uid="{DBC48131-1D65-499C-8B76-4E59D1299CE0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3488,76 +3509,76 @@
   <dimension ref="A1:Y50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="14" style="28" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="33.7109375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="34.7109375" style="28" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" style="28" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="21" style="29" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="37" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" style="17" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="18" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
+    <col min="5" max="5" width="34.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="21" style="20" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" style="25" customWidth="1"/>
+    <col min="11" max="11" width="9.85546875" style="10" customWidth="1"/>
+    <col min="12" max="12" width="30.140625" style="11" customWidth="1"/>
     <col min="13" max="13" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="79" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="75" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="87" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="33" t="s">
+      <c r="H1" s="82"/>
+      <c r="I1" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="34"/>
-      <c r="K1" s="38" t="s">
+      <c r="J1" s="84"/>
+      <c r="K1" s="85" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="39"/>
+      <c r="L1" s="86"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="77"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="40" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="I2" s="41" t="s">
+      <c r="I2" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="71" t="s">
+      <c r="K2" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="L2" s="72" t="s">
+      <c r="L2" s="53" t="s">
         <v>131</v>
       </c>
       <c r="M2" t="s">
@@ -3565,52 +3586,52 @@
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="42">
+      <c r="A3" s="28">
         <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="F3" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="46"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="51"/>
+      <c r="F3" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G3" s="32"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="37"/>
       <c r="N3" s="1">
         <f>M3*K3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="E4" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>135</v>
       </c>
       <c r="N4" s="1">
@@ -3619,31 +3640,31 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="31"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="17">
+      <c r="E5" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="12"/>
+      <c r="H5" s="21"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="10">
         <v>0.2472</v>
       </c>
-      <c r="L5" s="63" t="s">
+      <c r="L5" s="49" t="s">
         <v>195</v>
       </c>
       <c r="M5">
@@ -3655,28 +3676,28 @@
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="3">
         <v>10</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K6" s="17">
+      <c r="E6" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="10">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L6" s="63" t="s">
+      <c r="L6" s="49" t="s">
         <v>205</v>
       </c>
       <c r="M6">
@@ -3688,28 +3709,28 @@
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="3">
         <v>1</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K7" s="17">
+      <c r="E7" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K7" s="10">
         <v>5.6160000000000002E-2</v>
       </c>
-      <c r="L7" s="63" t="s">
+      <c r="L7" s="49" t="s">
         <v>204</v>
       </c>
       <c r="M7">
@@ -3721,28 +3742,28 @@
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="3">
         <v>2</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K8" s="17">
+      <c r="E8" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="10">
         <v>5.9389999999999998E-2</v>
       </c>
-      <c r="L8" s="63" t="s">
+      <c r="L8" s="49" t="s">
         <v>203</v>
       </c>
       <c r="M8">
@@ -3754,32 +3775,32 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="52">
+      <c r="A9" s="38">
         <v>3</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="54" t="s">
+      <c r="D9" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="F9" s="55" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="56"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
-      <c r="K9" s="60">
+      <c r="E9" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>135</v>
+      </c>
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="46">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L9" s="73" t="s">
+      <c r="L9" s="54" t="s">
         <v>206</v>
       </c>
       <c r="M9">
@@ -3791,18 +3812,18 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="90"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="92"/>
-      <c r="D10" s="92"/>
-      <c r="E10" s="92"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="95"/>
-      <c r="I10" s="94"/>
-      <c r="J10" s="96"/>
-      <c r="K10" s="94"/>
-      <c r="L10" s="97"/>
+      <c r="A10" s="67"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="70"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="70"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="72"/>
       <c r="M10" t="s">
         <v>220</v>
       </c>
@@ -3810,125 +3831,125 @@
         <f>SUM(N3:N9)</f>
         <v>33.854999999999997</v>
       </c>
-      <c r="O10" s="89"/>
-      <c r="P10" s="89"/>
-      <c r="Q10" s="89"/>
-      <c r="R10" s="89"/>
-      <c r="S10" s="89"/>
-      <c r="T10" s="89"/>
-      <c r="U10" s="89"/>
-      <c r="V10" s="89"/>
-      <c r="W10" s="89"/>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="66"/>
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66"/>
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+      <c r="W10" s="66"/>
+      <c r="X10" s="66"/>
+      <c r="Y10" s="66"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="16">
+      <c r="E11" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="12"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="9">
         <v>1.681</v>
       </c>
-      <c r="L11" s="78" t="s">
+      <c r="L11" s="57" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="3">
         <v>2</v>
       </c>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="K12" s="17">
+      <c r="E12" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="K12" s="10">
         <v>1.478</v>
       </c>
-      <c r="L12" s="63" t="s">
+      <c r="L12" s="49" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="2">
         <v>2</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="23" t="s">
+      <c r="E13" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="17">
+      <c r="I13" s="7"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="10">
         <v>0.98399999999999999</v>
       </c>
-      <c r="L13" s="63" t="s">
+      <c r="L13" s="49" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="3">
         <v>2</v>
       </c>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="9">
         <v>0.14940000000000001</v>
       </c>
-      <c r="L14" s="78" t="s">
+      <c r="L14" s="57" t="s">
         <v>226</v>
       </c>
       <c r="M14" t="s">
@@ -3936,508 +3957,508 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="3">
         <v>1</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="10">
         <v>0.1215</v>
       </c>
-      <c r="L15" s="63" t="s">
+      <c r="L15" s="49" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="3">
         <v>1</v>
       </c>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F16" s="27"/>
-      <c r="K16" s="17">
+      <c r="E16" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="K16" s="10">
         <v>2.5059999999999998</v>
       </c>
-      <c r="L16" s="63" t="s">
+      <c r="L16" s="49" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="3">
         <v>1</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F17" s="27" t="s">
+      <c r="E17" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="10">
         <v>1.0509999999999999</v>
       </c>
-      <c r="L17" s="63" t="s">
+      <c r="L17" s="49" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="3">
         <v>1</v>
       </c>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F18" s="27" t="s">
+      <c r="E18" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="10">
         <v>0.92500000000000004</v>
       </c>
-      <c r="L18" s="63" t="s">
+      <c r="L18" s="49" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="A19" s="3">
         <v>2</v>
       </c>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26" t="s">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="27" t="s">
+      <c r="E19" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="10">
         <v>2.25</v>
       </c>
-      <c r="L19" s="63" t="s">
+      <c r="L19" s="49" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="A20" s="3">
         <v>2</v>
       </c>
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="27" t="s">
+      <c r="E20" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="10">
         <v>1.236</v>
       </c>
-      <c r="L20" s="63" t="s">
+      <c r="L20" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="3">
         <v>2</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="27"/>
+      <c r="E21" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="19"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="3">
         <v>3</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26" t="s">
+      <c r="C22" s="18"/>
+      <c r="D22" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F22" s="27" t="s">
+      <c r="E22" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="10">
         <v>1.0469999999999999</v>
       </c>
-      <c r="L22" s="63" t="s">
+      <c r="L22" s="49" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="3">
         <v>1</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E23" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F23" s="27" t="s">
+      <c r="E23" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="10">
         <v>23.4</v>
       </c>
-      <c r="L23" s="63" t="s">
+      <c r="L23" s="49" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="A24" s="3">
         <v>1</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="15" t="s">
         <v>135</v>
       </c>
       <c r="F24" t="s">
         <v>172</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="13">
         <v>18.75</v>
       </c>
-      <c r="H24" s="98" t="s">
+      <c r="H24" s="73" t="s">
         <v>237</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="10">
         <v>0</v>
       </c>
-      <c r="L24" s="18" t="s">
+      <c r="L24" s="11" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="A25" s="3">
         <v>2</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="E25" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F25" s="26" t="s">
+      <c r="E25" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="10">
         <v>1.5349999999999999</v>
       </c>
-      <c r="L25" s="63" t="s">
+      <c r="L25" s="49" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="A26" s="3">
         <v>1</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26" t="s">
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18" t="s">
         <v>236</v>
       </c>
       <c r="F26" t="s">
         <v>242</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="13">
         <v>3.41</v>
       </c>
-      <c r="H26" s="98" t="s">
+      <c r="H26" s="73" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
-      <c r="F27" s="27"/>
+      <c r="A27" s="3"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="27"/>
+      <c r="A28" s="3"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="19"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="27"/>
+      <c r="A29" s="3"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="19"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
-      <c r="F30" s="27"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="19"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
-      <c r="F31" s="27"/>
+      <c r="A31" s="3"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="19"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="12" cm="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="5" cm="1">
         <f t="array" ref="G32">SUM(G11:G30*A11:A30)</f>
         <v>22.16</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="H32" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="K32" s="17" cm="1">
+      <c r="K32" s="10" cm="1">
         <f t="array" ref="K32">SUM(K11:K30*A11:A30)</f>
         <v>49.771299999999997</v>
       </c>
-      <c r="L32" s="18" t="s">
+      <c r="L32" s="11" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="27"/>
+      <c r="A33" s="3"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="19"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="27"/>
+      <c r="A34" s="3"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="19"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="27"/>
+      <c r="A35" s="3"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="19"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="27"/>
+      <c r="A36" s="3"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="19"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="27"/>
+      <c r="A37" s="3"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="19"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="26"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
-      <c r="F38" s="27"/>
+      <c r="A38" s="3"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="19"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="25"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="27"/>
+      <c r="A39" s="3"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="19"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="27"/>
+      <c r="A40" s="3"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="19"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="26"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="27"/>
+      <c r="A41" s="3"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="26"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="27"/>
+      <c r="A42" s="3"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="19"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="27"/>
+      <c r="A43" s="3"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="19"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="27"/>
+      <c r="A44" s="3"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="19"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="27"/>
+      <c r="A45" s="3"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="19"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="25"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="27"/>
+      <c r="A46" s="3"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="19"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="25"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="27"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="19"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="26"/>
-      <c r="F48" s="27"/>
+      <c r="A48" s="3"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="19"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="26"/>
-      <c r="F49" s="27"/>
+      <c r="A49" s="3"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="19"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="27"/>
+      <c r="A50" s="3"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4479,79 +4500,112 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58753BDD-603F-4060-8AE8-940A823D2E6E}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="74" t="s">
+        <v>246</v>
+      </c>
+      <c r="B2" s="106">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="106">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="74" t="s">
         <v>241</v>
       </c>
-      <c r="B2">
+      <c r="B4" s="106">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="100" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="74" t="s">
         <v>240</v>
       </c>
-      <c r="B3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="B5" s="106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="74" t="s">
         <v>239</v>
       </c>
-      <c r="B4">
+      <c r="B6" s="106">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="100" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="74" t="s">
+        <v>244</v>
+      </c>
+      <c r="B7" s="106">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="74" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="106">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="74" t="s">
         <v>238</v>
       </c>
-      <c r="B5">
+      <c r="B9" s="106">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="100" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="74" t="s">
         <v>237</v>
       </c>
-      <c r="B6">
+      <c r="B10" s="106">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="100" t="s">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="74" t="s">
         <v>242</v>
       </c>
-      <c r="B7">
-        <v>12</v>
+      <c r="B11" s="106">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{38454E2E-B1BE-46EF-BFE2-BB210E6FCC6C}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{60FBE8F9-7523-4577-ABCF-99B62829F7C3}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{087AF819-D1CD-4701-A4BC-81281096ACC8}"/>
-    <hyperlink ref="A2" r:id="rId4" xr:uid="{B5F647DA-2F1B-40BE-AD44-317720BD18EC}"/>
-    <hyperlink ref="A6" r:id="rId5" display="Wio-SX1262 " xr:uid="{F42343D2-42D5-40EB-9DBC-B5056D091598}"/>
-    <hyperlink ref="A7" r:id="rId6" xr:uid="{66EB5D16-345E-4639-BF59-600DE26B5E94}"/>
+    <hyperlink ref="A9" r:id="rId1" xr:uid="{36DBFE1F-CBB7-4A6C-9F4D-1D323B4DDAB8}"/>
+    <hyperlink ref="A6" r:id="rId2" xr:uid="{7E1680E9-04A1-42C2-B8E4-1E7B9CCFA71E}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{532463BC-6C0D-4F4D-9A6C-AB7E132D4201}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{1C6B81F5-F3A1-43F4-8705-3116B9E3BB90}"/>
+    <hyperlink ref="A7" r:id="rId5" display="DF40C-100DS-0.4V(51)" xr:uid="{4C3B22AB-8DDB-4EFE-B3B3-23CC7C96D794}"/>
+    <hyperlink ref="A8" r:id="rId6" xr:uid="{60F9D74B-72EE-49FD-ABD0-5A0BE4254318}"/>
+    <hyperlink ref="A2" r:id="rId7" xr:uid="{70DE18DB-856F-422F-AF2E-02990A1B2634}"/>
+    <hyperlink ref="A3" r:id="rId8" xr:uid="{878A7467-6179-4A24-8C7C-A3FF18669F9E}"/>
+    <hyperlink ref="A10" r:id="rId9" display="Wio-SX1262 " xr:uid="{2F1C45C3-8186-493A-A720-6D54E336F203}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{F7565900-56CA-4D3D-AD5A-A50CDC83F884}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BCC745-7B35-4308-85A8-4B8745FCF21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D9C42B-4691-4DFF-8C0A-2C4A4DFB5171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
     <sheet name="Top" sheetId="3" r:id="rId2"/>
-    <sheet name="MOUSER ZAMÓWIENIE" sheetId="4" r:id="rId3"/>
+    <sheet name="TME ZAMÓWIENIE" sheetId="7" r:id="rId3"/>
+    <sheet name="MOUSER ZAMÓWIENIE" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="252">
   <si>
     <t>Ilość</t>
   </si>
@@ -807,6 +808,15 @@
   </si>
   <si>
     <t>Aternatywa</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>Cena</t>
+  </si>
+  <si>
+    <t>Koszt</t>
   </si>
 </sst>
 </file>
@@ -841,7 +851,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -896,6 +906,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="45">
     <border>
@@ -1494,7 +1510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1551,7 +1567,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="27" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="39" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1568,8 +1583,44 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="43" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="44" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="22" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1591,7 +1642,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1600,16 +1651,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1621,24 +1663,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="34" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="38" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="26" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1984,8 +2008,8 @@
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="102" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="93" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="82" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="74" customWidth="1"/>
     <col min="10" max="10" width="30.140625" style="25" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" style="10" customWidth="1"/>
     <col min="12" max="12" width="30.140625" style="11" customWidth="1"/>
@@ -1993,51 +2017,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="106" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="108" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="99"/>
-      <c r="I1" s="83" t="s">
+      <c r="H1" s="109"/>
+      <c r="I1" s="110" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="85" t="s">
+      <c r="J1" s="111"/>
+      <c r="K1" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="86"/>
+      <c r="L1" s="99"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="88"/>
+      <c r="A2" s="107"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="101"/>
       <c r="G2" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="100" t="s">
+      <c r="H2" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="I2" s="94" t="s">
+      <c r="I2" s="75" t="s">
         <v>121</v>
       </c>
       <c r="J2" s="51" t="s">
@@ -2073,8 +2097,8 @@
         <v>135</v>
       </c>
       <c r="G3" s="32"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="95"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="76"/>
       <c r="J3" s="35"/>
       <c r="K3" s="36">
         <v>3.9190000000000003E-2</v>
@@ -2083,11 +2107,11 @@
         <v>196</v>
       </c>
       <c r="M3">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="N3" s="1">
         <f>K3*M3</f>
-        <v>0.47028000000000003</v>
+        <v>1.6459800000000002</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -2536,7 +2560,7 @@
       <c r="K17" s="10">
         <v>1.093</v>
       </c>
-      <c r="L17" s="58" t="s">
+      <c r="L17" s="57" t="s">
         <v>230</v>
       </c>
       <c r="M17">
@@ -2563,7 +2587,7 @@
       <c r="K18" s="10">
         <v>0.29389999999999999</v>
       </c>
-      <c r="L18" s="58" t="s">
+      <c r="L18" s="57" t="s">
         <v>232</v>
       </c>
       <c r="M18">
@@ -2618,47 +2642,47 @@
         <v>37</v>
       </c>
       <c r="G20" s="42"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="96"/>
+      <c r="H20" s="83"/>
+      <c r="I20" s="77"/>
       <c r="J20" s="45"/>
       <c r="K20" s="46"/>
       <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A21" s="59"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="61"/>
-      <c r="D21" s="61"/>
-      <c r="E21" s="61"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="63"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="62"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="65"/>
+      <c r="A21" s="58"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="61"/>
+      <c r="K21" s="63"/>
+      <c r="L21" s="64"/>
       <c r="M21" t="s">
         <v>218</v>
       </c>
       <c r="N21" s="1">
         <f>SUM(N3:N20)</f>
-        <v>61.496720000000003</v>
-      </c>
-      <c r="O21" s="66"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="66"/>
-      <c r="V21" s="66"/>
-      <c r="W21" s="66"/>
-      <c r="X21" s="66"/>
-      <c r="Y21" s="66"/>
-      <c r="Z21" s="66"/>
-      <c r="AA21" s="66"/>
-      <c r="AB21" s="66"/>
-      <c r="AC21" s="66"/>
+        <v>62.67242000000001</v>
+      </c>
+      <c r="O21" s="65"/>
+      <c r="P21" s="65"/>
+      <c r="Q21" s="65"/>
+      <c r="R21" s="65"/>
+      <c r="S21" s="65"/>
+      <c r="T21" s="65"/>
+      <c r="U21" s="65"/>
+      <c r="V21" s="65"/>
+      <c r="W21" s="65"/>
+      <c r="X21" s="65"/>
+      <c r="Y21" s="65"/>
+      <c r="Z21" s="65"/>
+      <c r="AA21" s="65"/>
+      <c r="AB21" s="65"/>
+      <c r="AC21" s="65"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -2732,8 +2756,8 @@
         <v>135</v>
       </c>
       <c r="G24" s="12"/>
-      <c r="H24" s="105"/>
-      <c r="I24" s="98"/>
+      <c r="H24" s="85"/>
+      <c r="I24" s="79"/>
       <c r="J24" s="24"/>
       <c r="K24" s="10">
         <v>2.2789999999999999</v>
@@ -2743,116 +2767,116 @@
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="86">
         <v>2</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="90">
         <v>0.38300000000000001</v>
       </c>
-      <c r="H25" s="106" t="s">
+      <c r="H25" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="I25" s="93">
+      <c r="I25" s="92">
         <v>1.65</v>
       </c>
-      <c r="J25" s="56">
+      <c r="J25" s="93">
         <v>3434715</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="90">
         <v>0</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="94" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="86">
         <v>1</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="88" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="88" t="s">
         <v>103</v>
       </c>
-      <c r="F26" s="19" t="s">
+      <c r="F26" s="89" t="s">
         <v>123</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="90">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H26" s="106" t="s">
+      <c r="H26" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="I26" s="93">
+      <c r="I26" s="92">
         <v>1.64</v>
       </c>
-      <c r="J26" s="56">
+      <c r="J26" s="93">
         <v>3434712</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="90">
         <v>0</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="94" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="A27" s="86">
         <v>2</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="88" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="F27" s="19" t="s">
+      <c r="F27" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="90">
         <v>5.68</v>
       </c>
-      <c r="H27" s="106" t="s">
+      <c r="H27" s="91" t="s">
         <v>241</v>
       </c>
-      <c r="I27" s="93">
+      <c r="I27" s="92">
         <v>7.17</v>
       </c>
-      <c r="J27" s="56">
+      <c r="J27" s="93">
         <v>2300373</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="90">
         <v>0</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="94" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2964,116 +2988,116 @@
       </c>
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
+      <c r="A32" s="86">
         <v>1</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="88" t="s">
         <v>111</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="F32" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="G32" s="13">
+      <c r="G32" s="90">
         <v>7.7</v>
       </c>
-      <c r="H32" s="106" t="s">
+      <c r="H32" s="91" t="s">
         <v>240</v>
       </c>
-      <c r="I32" s="93">
+      <c r="I32" s="92">
         <v>8.82</v>
       </c>
-      <c r="J32" s="56">
+      <c r="J32" s="93">
         <v>2614867</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="90">
         <v>0</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="94" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="3">
+      <c r="A33" s="86">
         <v>1</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="88" t="s">
         <v>90</v>
       </c>
-      <c r="E33" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="F33" s="19" t="s">
+      <c r="E33" s="88" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="13">
+      <c r="G33" s="90">
         <v>1.7</v>
       </c>
-      <c r="H33" s="106" t="s">
+      <c r="H33" s="91" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="93">
+      <c r="I33" s="92">
         <v>2.52</v>
       </c>
-      <c r="J33" s="56">
+      <c r="J33" s="93">
         <v>4216300</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="90">
         <v>0</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="94" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="3">
+      <c r="A34" s="86">
         <v>2</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="88" t="s">
         <v>91</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="88" t="s">
         <v>112</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="F34" s="89" t="s">
         <v>175</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="90">
         <v>5.5529999999999999</v>
       </c>
-      <c r="H34" s="106" t="s">
+      <c r="H34" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="I34" s="93">
+      <c r="I34" s="92">
         <v>7.43</v>
       </c>
-      <c r="J34" s="56">
+      <c r="J34" s="93">
         <v>4137104</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="90">
         <v>0</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="94" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3130,78 +3154,78 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="3">
+      <c r="A37" s="86">
         <v>1</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="87" t="s">
         <v>68</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="F37" s="19" t="s">
+      <c r="F37" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="G37" s="13">
+      <c r="G37" s="90">
         <v>1.04</v>
       </c>
-      <c r="H37" s="106" t="s">
+      <c r="H37" s="91" t="s">
         <v>245</v>
       </c>
-      <c r="I37" s="93">
+      <c r="I37" s="92">
         <v>1.5</v>
       </c>
-      <c r="J37" s="56">
+      <c r="J37" s="93">
         <v>2575555</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="90">
         <v>0</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="94" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="3">
+      <c r="A38" s="86">
         <v>1</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="87" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="88" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="F38" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="90">
         <v>1.19</v>
       </c>
-      <c r="H38" s="106" t="s">
+      <c r="H38" s="91" t="s">
         <v>238</v>
       </c>
-      <c r="I38" s="93">
+      <c r="I38" s="92">
         <v>0</v>
       </c>
-      <c r="J38" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="K38" s="10">
+      <c r="J38" s="89" t="s">
+        <v>135</v>
+      </c>
+      <c r="K38" s="90">
         <v>0</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="94" t="s">
         <v>135</v>
       </c>
       <c r="M38" t="s">
@@ -3294,7 +3318,7 @@
       <c r="H45" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I45" s="93" cm="1">
+      <c r="I45" s="74" cm="1">
         <f t="array" ref="I45">SUM(I22:I44*A22:A44)</f>
         <v>46.980000000000004</v>
       </c>
@@ -3453,15 +3477,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="I1:J1"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="I1:J1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L3" r:id="rId1" tooltip="04025C104KAT2A; Kondensator: ceramiczny; MLCC; 100nF; 50V; X7R; ±10%; SMD; 0402" display="https://www.tme.eu/pl/details/04025c104kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{4885974C-EAC2-4390-9084-66DCF3F94398}"/>
@@ -3530,44 +3554,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="106" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="77" t="s">
+      <c r="B1" s="104" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="102" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="100" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="81" t="s">
+      <c r="G1" s="108" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="82"/>
-      <c r="I1" s="83" t="s">
+      <c r="H1" s="112"/>
+      <c r="I1" s="110" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="84"/>
-      <c r="K1" s="85" t="s">
+      <c r="J1" s="111"/>
+      <c r="K1" s="98" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="86"/>
+      <c r="L1" s="99"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="80"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="91"/>
+      <c r="A2" s="107"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
       <c r="G2" s="26" t="s">
         <v>121</v>
       </c>
@@ -3817,18 +3841,18 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="67"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="70"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="69"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="70"/>
-      <c r="K10" s="71"/>
-      <c r="L10" s="72"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
       <c r="M10" t="s">
         <v>220</v>
       </c>
@@ -3836,17 +3860,17 @@
         <f>SUM(N3:N9)</f>
         <v>33.854999999999997</v>
       </c>
-      <c r="O10" s="66"/>
-      <c r="P10" s="66"/>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-      <c r="T10" s="66"/>
-      <c r="U10" s="66"/>
-      <c r="V10" s="66"/>
-      <c r="W10" s="66"/>
-      <c r="X10" s="66"/>
-      <c r="Y10" s="66"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="65"/>
+      <c r="Q10" s="65"/>
+      <c r="R10" s="65"/>
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -3874,7 +3898,7 @@
       <c r="K11" s="9">
         <v>1.681</v>
       </c>
-      <c r="L11" s="57" t="s">
+      <c r="L11" s="56" t="s">
         <v>208</v>
       </c>
     </row>
@@ -3954,7 +3978,7 @@
       <c r="K14" s="9">
         <v>0.14940000000000001</v>
       </c>
-      <c r="L14" s="57" t="s">
+      <c r="L14" s="56" t="s">
         <v>226</v>
       </c>
       <c r="M14" t="s">
@@ -4088,48 +4112,58 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="86">
         <v>2</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="87" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="88" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F20" s="19" t="s">
+      <c r="E20" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20" s="89" t="s">
         <v>155</v>
       </c>
-      <c r="K20" s="10">
+      <c r="G20" s="90"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="90"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="90">
         <v>1.236</v>
       </c>
-      <c r="L20" s="49" t="s">
+      <c r="L20" s="91" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="86">
         <v>2</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="87" t="s">
         <v>143</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="88" t="s">
         <v>156</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="88" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F21" s="19"/>
+      <c r="E21" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="89"/>
+      <c r="G21" s="90"/>
+      <c r="H21" s="88"/>
+      <c r="I21" s="90"/>
+      <c r="J21" s="89"/>
+      <c r="K21" s="90"/>
+      <c r="L21" s="94"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
@@ -4182,34 +4216,36 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="86">
         <v>1</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="87" t="s">
         <v>149</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="88" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="E24" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" s="96" t="s">
         <v>172</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="90">
         <v>18.75</v>
       </c>
-      <c r="H24" s="73" t="s">
+      <c r="H24" s="97" t="s">
         <v>237</v>
       </c>
-      <c r="K24" s="10">
+      <c r="I24" s="90"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="90">
         <v>0</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="94" t="s">
         <v>135</v>
       </c>
     </row>
@@ -4240,24 +4276,28 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="86">
         <v>1</v>
       </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18" t="s">
+      <c r="B26" s="87"/>
+      <c r="C26" s="88"/>
+      <c r="D26" s="88"/>
+      <c r="E26" s="88" t="s">
         <v>236</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="96" t="s">
         <v>242</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="90">
         <v>3.41</v>
       </c>
-      <c r="H26" s="73" t="s">
+      <c r="H26" s="97" t="s">
         <v>242</v>
       </c>
+      <c r="I26" s="90"/>
+      <c r="J26" s="89"/>
+      <c r="K26" s="90"/>
+      <c r="L26" s="94"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
@@ -4504,6 +4544,691 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D8C8C9-3DB7-45D8-9874-7FAF2F9722AF}">
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="72" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3.9190000000000003E-2</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*C2</f>
+        <v>1.2540800000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.20480000000000001</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D41" si="0">B3*C3</f>
+        <v>2.048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="72" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.18210000000000001</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>1.8210000000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.1421</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>1.421</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4.1669999999999999E-2</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.41669999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1">
+        <v>0.28220000000000001</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="72" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>3.3119999999999997E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>3.3119999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="72" t="s">
+        <v>200</v>
+      </c>
+      <c r="B9">
+        <v>100</v>
+      </c>
+      <c r="C9" s="1">
+        <v>3.9050000000000001E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>3.9050000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10">
+        <v>100</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1.7569999999999999E-2</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>1.7569999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="72" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3.6560000000000002E-2</v>
+      </c>
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>3.6560000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.21560000000000001</v>
+      </c>
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>2.1560000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="72" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5.9389999999999998E-2</v>
+      </c>
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>5.9390000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="72" t="s">
+        <v>197</v>
+      </c>
+      <c r="B14">
+        <v>100</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6.7129999999999995E-2</v>
+      </c>
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>6.7129999999999992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="72" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.093</v>
+      </c>
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16" s="1">
+        <v>0.29389999999999999</v>
+      </c>
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>4.7023999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17">
+        <v>50</v>
+      </c>
+      <c r="C17" s="1">
+        <v>0.2472</v>
+      </c>
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>12.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="72" t="s">
+        <v>205</v>
+      </c>
+      <c r="B18">
+        <v>100</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="72" t="s">
+        <v>204</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.6160000000000002E-2</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>5.6160000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="B20">
+        <v>100</v>
+      </c>
+      <c r="C20" s="1">
+        <v>5.9389999999999998E-2</v>
+      </c>
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>5.9390000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="72" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21">
+        <v>100</v>
+      </c>
+      <c r="C21" s="1">
+        <v>4.9700000000000001E-2</v>
+      </c>
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="72" t="s">
+        <v>225</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3.7360000000000002</v>
+      </c>
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>37.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="72" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23">
+        <v>16</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1.643</v>
+      </c>
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>26.288</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="72" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.2789999999999999</v>
+      </c>
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>22.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="72" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>8.41</v>
+      </c>
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>50.46</v>
+      </c>
+      <c r="F25" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="72" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26">
+        <v>16</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.5059999999999998</v>
+      </c>
+      <c r="D26" s="1">
+        <f t="shared" si="0"/>
+        <v>40.095999999999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="72" t="s">
+        <v>187</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1">
+        <v>9.67</v>
+      </c>
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>58.019999999999996</v>
+      </c>
+      <c r="F27" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="72" t="s">
+        <v>188</v>
+      </c>
+      <c r="B28">
+        <v>10</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1.4419999999999999</v>
+      </c>
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>14.42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="72" t="s">
+        <v>176</v>
+      </c>
+      <c r="B29">
+        <v>32</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.0469999999999999</v>
+      </c>
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>33.503999999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="72" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1.45</v>
+      </c>
+      <c r="D30" s="1">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1">
+        <v>7.11</v>
+      </c>
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>71.100000000000009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="72" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32">
+        <v>16</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1.681</v>
+      </c>
+      <c r="D32" s="1">
+        <f t="shared" si="0"/>
+        <v>26.896000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33">
+        <v>16</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1.478</v>
+      </c>
+      <c r="D33" s="1">
+        <f t="shared" si="0"/>
+        <v>23.648</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="B34">
+        <v>16</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>15.744</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="B35">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.14940000000000001</v>
+      </c>
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>1.494</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="72" t="s">
+        <v>227</v>
+      </c>
+      <c r="B36">
+        <v>10</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.1215</v>
+      </c>
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>1.2149999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="72" t="s">
+        <v>233</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="B38">
+        <v>10</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39">
+        <v>16</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1">
+        <v>23.4</v>
+      </c>
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>187.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41">
+        <v>16</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1.5349999999999999</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>24.56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>218</v>
+      </c>
+      <c r="D44" s="1">
+        <f>SUM(D2:D41)</f>
+        <v>803.05118000000016</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" tooltip="04025C104KAT2A; Kondensator: ceramiczny; MLCC; 100nF; 50V; X7R; ±10%; SMD; 0402" display="https://www.tme.eu/pl/details/04025c104kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{920C6B2B-B6C1-4CB0-ABF0-CB2F0D8427D2}"/>
+    <hyperlink ref="A3" r:id="rId2" tooltip="08055A330KAT2A; Kondensator: ceramiczny; MLCC; 33pF; 50V; C0G (NP0); ±10%; SMD; 0805" display="https://www.tme.eu/pl/details/08055a330kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{FA903295-2780-49B3-B5D8-71D528918A78}"/>
+    <hyperlink ref="A4" r:id="rId3" tooltip="08055C272KAT2A; Kondensator: ceramiczny; MLCC; 2,7nF; 50V; X7R; ±10%; SMD; 0805" display="https://www.tme.eu/pl/details/08055c272kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{1E1E1090-FDBE-48AD-B9FC-583960077F76}"/>
+    <hyperlink ref="A5" r:id="rId4" tooltip="08055C103KAT2A; Kondensator: ceramiczny; MLCC; 10nF; 50V; X7R; ±10%; SMD; 0805; 180mm" display="https://www.tme.eu/pl/details/08055c103kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{D2B5537D-EAE8-4AD8-8B43-2D48100486DB}"/>
+    <hyperlink ref="A6" r:id="rId5" tooltip="08055C104KAT2A; Kondensator: ceramiczny; MLCC; 100nF; 50V; X7R; ±10%; SMD; 0805" display="https://www.tme.eu/pl/details/08055c104kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{8317FBD3-FFA0-48D7-A069-BC4A93B23F97}"/>
+    <hyperlink ref="A7" r:id="rId6" tooltip="08055C105KAT2A; Kondensator: ceramiczny; MLCC; 1uF; 50V; X7R; ±10%; SMD; 0805; 180mm" display="https://www.tme.eu/pl/details/08055c105kat2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{1F6246E5-1636-4497-947E-C817EDEC0551}"/>
+    <hyperlink ref="A8" r:id="rId7" tooltip="SMD0402-1K-1%; Rezystor: thick film; SMD; 0402; 1kΩ; 62,5mW; ±1%; 50V; -55÷155°C" display="https://www.tme.eu/pl/details/smd0402-1k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0402wgf1001tce/" xr:uid="{C71C74B4-B48C-421F-9AA6-76BD203AEB95}"/>
+    <hyperlink ref="A9" r:id="rId8" tooltip="SMD0402-2K2-1%; Rezystor: thick film; SMD; 0402; 2,2kΩ; 62,5mW; ±1%; 50V; -55÷155°C" display="https://www.tme.eu/pl/details/smd0402-2k2-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0402wgf2201tce/" xr:uid="{7331AA85-E138-4DB2-A27B-BA555DC345A7}"/>
+    <hyperlink ref="A10" r:id="rId9" tooltip="SMD0402-10K-1%; Rezystor: thick film; SMD; 0402; 10kΩ; 62,5mW; ±1%; 50V; -55÷155°C" display="https://www.tme.eu/pl/details/smd0402-10k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0402wgf1002tce/" xr:uid="{0A90FF7F-5247-4046-8A89-3ED52FE31993}"/>
+    <hyperlink ref="A11" r:id="rId10" tooltip="SMD0402-15K-1%; Rezystor: thick film; SMD; 0402; 15kΩ; 62,5mW; ±1%; 50V; -55÷155°C" display="https://www.tme.eu/pl/details/smd0402-15k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0402wgf1502tce/" xr:uid="{5B86AEC2-F840-4B2E-8D2C-0E4F62441447}"/>
+    <hyperlink ref="A12" r:id="rId11" tooltip="ERA6AEB1153V; Rezystor: thin film; SMD; 0805; 115kΩ; 125mW; ±0,1%; ERA6AEB" display="https://www.tme.eu/pl/details/era6aeb1153v/rezystory-smd/panasonic-industry-europe-gmbh/" xr:uid="{2CD8BA1F-7752-4E51-B89B-69AD1545B799}"/>
+    <hyperlink ref="A13" r:id="rId12" tooltip="SMD0805-22K1-1%; Rezystor: thick film; SMD; 0805; 22,1kΩ; 0,125W; ±1%; 150V" display="https://www.tme.eu/pl/details/smd0805-22k1-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f2212t5e/" xr:uid="{6C7503D1-60A0-4CC6-B7B4-3B97BC66BBD8}"/>
+    <hyperlink ref="A14" r:id="rId13" tooltip="SMD0805-15.8K-1%; Rezystor: thick film; SMD; 0805; 15,8kΩ; 0,125W; ±1%; 150V" display="https://www.tme.eu/pl/details/smd0805-15.8k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f1582t5e/" xr:uid="{5BADE0FC-CE9C-41AE-AA2E-ADC34E2EA61A}"/>
+    <hyperlink ref="A15" r:id="rId14" tooltip="ZL303-2X40P; Złącze: kołkowe; listwa kołkowa; męskie; PIN: 80; THT; proste; 2mm" display="https://www.tme.eu/pl/details/zl303-2x40p/listwy-i-gniazda-kolkowe/connfly/ds1025-05-2x40p8bv1-b/" xr:uid="{30C92EDD-4FD5-45A4-A1D6-89A5F093FEC0}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{0527F2E6-225B-4BBC-87B4-E2D1DC28E1F3}"/>
+    <hyperlink ref="A20" r:id="rId16" tooltip="SMD0805-5K1-1%; Rezystor: thick film; SMD; 0805; 5,1kΩ; 0,125W; ±1%; 150V; -55÷125°C" display="https://www.tme.eu/pl/details/smd0805-5k1-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f5101t5e/" xr:uid="{F4B2CC5D-50EE-4754-8829-7541D6320EF4}"/>
+    <hyperlink ref="A19" r:id="rId17" tooltip="SMD0805-2K2-1%; Rezystor: thick film; SMD; 0805; 2,2kΩ; 0,125W; ±1%; 150V; -55÷125°C" display="https://www.tme.eu/pl/details/smd0805-2k2-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f2201t5e/" xr:uid="{3CFAF855-B43B-4B7F-B937-A4AA79DDDC70}"/>
+    <hyperlink ref="A18" r:id="rId18" tooltip="SMD0805-1K-1%; Rezystor: thick film; SMD; 0805; 1kΩ; 0,125W; ±1%; 150V; -55÷125°C" display="https://www.tme.eu/pl/details/smd0805-1k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f1001t5e/" xr:uid="{EEB852A0-4D32-428F-A6F5-FF858243643C}"/>
+    <hyperlink ref="A17" r:id="rId19" tooltip="08055C474K4T2A; Kondensator: ceramiczny; MLCC; 470nF; 50V; X7R; ±10%; SMD; 0805" display="https://www.tme.eu/pl/details/08055c474k4t2a/kondensatory-mlcc-smd/kyocera-avx/" xr:uid="{84D36213-FF68-4DFB-9DFB-85812A9AC11C}"/>
+    <hyperlink ref="A21" r:id="rId20" tooltip="SMD0805-10K-1%; Rezystor: thick film; SMD; 0805; 10kΩ; 0,125W; ±1%; 150V; -55÷125°C" display="https://www.tme.eu/pl/details/smd0805-10k-1%25/rezystory-smd/royalohm-royal-electronic-fty-co/0805s8f1002t5e/" xr:uid="{C32F253F-C13B-4951-9ED4-F395F7986C36}"/>
+    <hyperlink ref="A25" r:id="rId21" tooltip="MX-503398-1892; Złącze: do kart; microSD; push-push; SMT; złocony; PIN: 8" display="https://www.tme.eu/pl/details/mx-503398-1892/zlacza-do-kart/molex-interconnect-gmbh/503398-1892/" xr:uid="{64320705-13EC-41CC-887A-8576D451FA53}"/>
+    <hyperlink ref="A27" r:id="rId22" tooltip="MX-48393-0003; Złącze: USB A; gniazdo; na PCB; THT; PIN: 9; kątowe 90°; USB 3.0" display="https://www.tme.eu/pl/details/mx-48393-0003/zlacza-usb-i-ieee1394/molex-interconnect-gmbh/48393-0003/" xr:uid="{268A252F-1A1A-4B79-828C-3A3961BF698E}"/>
+    <hyperlink ref="A28" r:id="rId23" tooltip="SM04B-SRSS-TB; Złącze: przewód-płytka; gniazdo; męskie; 1A; 50V; PIN: 4; SMT; 1mm" display="https://www.tme.eu/pl/details/sm04b-srss-tb/zlacza-sygnalowe-raster-1-00mm/jst-j-s-t-deutschland-gmbh/sm04b-srss-tb-lf-sn/" xr:uid="{AF23A38C-DEFA-4C39-B906-C2E38476677A}"/>
+    <hyperlink ref="A29" r:id="rId24" tooltip="KMR221GLFS; Mikroprzełącznik TACT; SPST-NO; Poz: 2; 0,05A/32VDC; SMT; brak; 2N" display="https://www.tme.eu/pl/details/kmr221glfs/mikroprzelaczniki-tact/c-k-components-sas/kmr221g-lfs/" xr:uid="{3FC96E5D-0B56-4A15-9DF3-1D8A0C31F5DF}"/>
+    <hyperlink ref="A30" r:id="rId25" tooltip="AP22653W6-7; IC: power switch; high-side,USB switch; 2,1A; Ch: 1; P-Channel; SMD" display="https://www.tme.eu/pl/details/ap22653w6-7/power-switches-uklady-scalone/diodes-incorporated/" xr:uid="{ADFAE75C-37F8-48B2-9346-A2CE139C8872}"/>
+    <hyperlink ref="A31" r:id="rId26" tooltip="AP64501SP-13; PMIC; przetwornica DC/DC; Uwej: 3,8÷40VDC; Uwyj: 0,8÷39VDC; 5A" display="https://www.tme.eu/pl/details/ap64501sp-13/regulatory-napiecia-uklady-dc-dc/diodes-incorporated/" xr:uid="{F6BD960D-9FC2-49E5-BD06-B09B8380E0B2}"/>
+    <hyperlink ref="A23" r:id="rId27" tooltip="TAJB226K016R; Kondensator: tantalowy; 22uF; 16VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb226k016r/kondensatory-tantalowe-smd/kyocera-avx/tajb226k016rnj/" xr:uid="{491AF004-F2C2-46A5-BEE4-20A2B6AE5010}"/>
+    <hyperlink ref="A24" r:id="rId28" tooltip="TAJD106K035R; Kondensator: tantalowy; 10uF; 35VDC; SMD; D; 2917; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajd106k035r/kondensatory-tantalowe-smd/kyocera-avx/tajd106k035rnj/" xr:uid="{0B4F6D00-E202-4BA4-8FDB-804856846287}"/>
+    <hyperlink ref="A22" r:id="rId29" tooltip="TAJC106K035R; Kondensator: tantalowy; 10uF; 35VDC; SMD; C; 2312; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajc106k035r/kondensatory-tantalowe-smd/kyocera-avx/tajc106k035rnj/" xr:uid="{46C22877-23D6-45C5-AEDA-2CC90A8239AD}"/>
+    <hyperlink ref="A26" r:id="rId30" tooltip="USB4105-GF-A-060; Złącze: USB C; gniazdo; SMT; PIN: 16; pozioma; top board mount; 5A" display="https://www.tme.eu/pl/details/usb4105-gf-a-060/zlacza-usb-i-ieee1394/gct/" xr:uid="{BC56821A-ED0C-44B7-883E-FB9146976695}"/>
+    <hyperlink ref="A34" r:id="rId31" tooltip="MBR1020VL-AU-R1; Dioda: prostownicza Schottky; SOD123F; SMD; 20V; 1A; rolka,taśma" display="https://www.tme.eu/pl/details/mbr1020vl-au-r1/diody-schottky-smd/panjit-semiconductor-panjit-international-inc/mbr1020vl-au-r1-000a1/" xr:uid="{7860B95D-68B8-4D8A-9A41-A3057F22A5C6}"/>
+    <hyperlink ref="A35" r:id="rId32" tooltip="LTST-C190KRKT; LED; czerwony; SMD; 0603; 18÷180mcd; 1,6÷2,4VDC; 1,6x0,8x0,8mm" display="https://www.tme.eu/pl/details/ltst-c190krkt/diody-led-smd-kolorowe/lite-on-technology/" xr:uid="{071A3C24-7C48-4CA1-BF21-B2F8C58882BA}"/>
+    <hyperlink ref="A36" r:id="rId33" tooltip="LTST-C190KGKT; LED; zielony; SMD; 0603; 18÷71mcd; 1,9÷2,4VDC; 1,6x0,8x0,8mm; 130°" display="https://www.tme.eu/pl/details/ltst-c190kgkt/diody-led-smd-kolorowe/lite-on-technology/" xr:uid="{2C6588DA-B5DE-41BD-8395-636020347DFC}"/>
+    <hyperlink ref="A38" r:id="rId34" tooltip="MX-53048-0210; Złącze: przewód-płytka; gniazdo; męskie; PIN: 2; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0210/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0210/" xr:uid="{A9F73556-C8E2-47D6-AE19-8423F64F81A0}"/>
+    <hyperlink ref="A39" r:id="rId35" tooltip="MX-53048-0810; Złącze: przewód-płytka; gniazdo; męskie; PIN: 8; PicoBlade™; THT" display="https://www.tme.eu/pl/details/mx-53048-0810/zlacza-sygnalowe-raster-1-25mm/molex-interconnect-gmbh/53048-0810/" xr:uid="{2B872281-7A52-4335-9413-6CDA68727DFE}"/>
+    <hyperlink ref="A40" r:id="rId36" tooltip="ESP32S3-WRM1U-16R8; Moduł: IoT; Bluetooth: BLE; WiFi; zewnętrzna; IEEE 802.11b/g/n" display="https://www.tme.eu/pl/details/esp32s3-wrm1u-16r8/moduly-iot-wifi-bluetooth/espressif-systems/esp32-s3-wroom-1u-n16r8/" xr:uid="{278E538D-5A83-4B2E-9C52-2802E545DE4E}"/>
+    <hyperlink ref="A41" r:id="rId37" tooltip="AP7361C-33E-13; IC: stabilizator napięcia; LDO,liniowy,nieregulowany; 3,3V; 1A" display="https://www.tme.eu/pl/details/ap7361c-33e-13/stabilizatory-napiecia-nieregulowane-ldo/diodes-incorporated/" xr:uid="{69E7866B-FE73-48A9-8E28-DF80C7ED686E}"/>
+    <hyperlink ref="A32" r:id="rId38" tooltip="TAJB475K035R; Kondensator: tantalowy; 4,7uF; 35VDC; SMD; B; 1411; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/tajb475k035r/kondensatory-tantalowe-smd/kyocera-avx/tajb475k035rnj/" xr:uid="{DFAB0C15-4E09-40B4-9F70-3BF387EF1F8F}"/>
+    <hyperlink ref="A33" r:id="rId39" tooltip="TAJA475K010R; Kondensator: tantalowy; 4,7uF; 10VDC; SMD; A; 1206; ±10%; -55÷125°C" display="https://www.tme.eu/pl/details/taja475k010r/kondensatory-tantalowe-smd/kyocera-avx/taja475k010rnj/" xr:uid="{A433F268-7F08-47B5-95E7-48008C0A0208}"/>
+    <hyperlink ref="A37" r:id="rId40" tooltip="MX-53047-0310; Złącze: przewód-płytka; gniazdo; męskie; PIN: 3; PicoBlade™; proste" display="https://www.tme.eu/pl/details/mx-53047-0310/zlacza-sygnalowe-raster-1-25mm/molex/53047-0310/" xr:uid="{161FA093-8F67-47EC-8C4D-F7DC54558080}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58753BDD-603F-4060-8AE8-940A823D2E6E}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4520,85 +5245,85 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="72" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="107">
+      <c r="B2">
         <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="72" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="107">
+      <c r="B3">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="72" t="s">
         <v>241</v>
       </c>
-      <c r="B4" s="107">
+      <c r="B4">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="72" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="107">
+      <c r="B5">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="72" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="107">
+      <c r="B6">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="72" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="107">
+      <c r="B7">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="72" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="107">
+      <c r="B8">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="72" t="s">
         <v>238</v>
       </c>
-      <c r="B9" s="107">
+      <c r="B9">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="74" t="s">
+      <c r="A10" s="72" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="107">
+      <c r="B10">
         <v>12</v>
       </c>
-      <c r="E10" s="92" t="s">
+      <c r="E10" s="73" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="74" t="s">
+      <c r="A11" s="72" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="107">
+      <c r="B11">
         <v>14</v>
       </c>
     </row>

--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D9C42B-4691-4DFF-8C0A-2C4A4DFB5171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD108B92-E698-4CEB-89CB-2782784DAF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
     <sheet name="Top" sheetId="3" r:id="rId2"/>
     <sheet name="TME ZAMÓWIENIE" sheetId="7" r:id="rId3"/>
     <sheet name="MOUSER ZAMÓWIENIE" sheetId="4" r:id="rId4"/>
+    <sheet name="Mouser zamówienie dodatkowe" sheetId="8" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="274">
   <si>
     <t>Ilość</t>
   </si>
@@ -817,6 +818,72 @@
   </si>
   <si>
     <t>Koszt</t>
+  </si>
+  <si>
+    <t>Mistake has been made here - this is 10uF instead of 100uF. Soldered anyway.</t>
+  </si>
+  <si>
+    <t>10nF was not available. Soldered from private stash.</t>
+  </si>
+  <si>
+    <t>Here also is a mistake - should be 10uF, is 1uF. Soldered from private stash.</t>
+  </si>
+  <si>
+    <t>CM5 Dev board</t>
+  </si>
+  <si>
+    <t>Kabel Micro HDMI</t>
+  </si>
+  <si>
+    <t>Złącza Micro HDMI</t>
+  </si>
+  <si>
+    <t>Złącza ZIF do MIPI</t>
+  </si>
+  <si>
+    <t>Tantale pod USB - KEMET D 100uF</t>
+  </si>
+  <si>
+    <t>Ilość po uwzględnieniu progów cenowych</t>
+  </si>
+  <si>
+    <t>Ilość docelowa</t>
+  </si>
+  <si>
+    <t>USB A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358-SC0358 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">538-46765-0301 </t>
+  </si>
+  <si>
+    <t>Nr prod MOUSER</t>
+  </si>
+  <si>
+    <t>&lt;-</t>
+  </si>
+  <si>
+    <t>TYLE OSTATECZNIE ZAMÓWIĆ!</t>
+  </si>
+  <si>
+    <t>Nie ma w mouser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667-EEF-CX0J101R </t>
+  </si>
+  <si>
+    <t>80-C0805C106M8RAUTLR</t>
+  </si>
+  <si>
+    <t>Kondensator 10uF 10V 0805</t>
+  </si>
+  <si>
+    <t>GRM21BR60J107ME15L</t>
+  </si>
+  <si>
+    <t>100nF 0805</t>
   </si>
 </sst>
 </file>
@@ -1609,24 +1676,6 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1649,6 +1698,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2002,7 +2069,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
     <col min="4" max="4" width="33.7109375" customWidth="1"/>
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
@@ -2016,45 +2083,45 @@
     <col min="13" max="13" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="100" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="110" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="108" t="s">
+      <c r="G1" s="102" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="109"/>
-      <c r="I1" s="110" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="98" t="s">
+      <c r="J1" s="105"/>
+      <c r="K1" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="99"/>
-    </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="101"/>
+      <c r="L1" s="107"/>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="101"/>
+      <c r="B2" s="99"/>
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="109"/>
       <c r="G2" s="50" t="s">
         <v>121</v>
       </c>
@@ -2077,7 +2144,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="28">
         <v>4</v>
       </c>
@@ -2114,7 +2181,7 @@
         <v>1.6459800000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -2147,7 +2214,7 @@
         <v>2.4576000000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -2180,7 +2247,7 @@
         <v>2.1852</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -2212,8 +2279,11 @@
         <f t="shared" si="0"/>
         <v>1.7052</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -2246,7 +2316,7 @@
         <v>0.50004000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -2278,8 +2348,11 @@
         <f t="shared" si="0"/>
         <v>11.852399999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -2312,7 +2385,7 @@
         <v>3.3119999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>4</v>
       </c>
@@ -2345,7 +2418,7 @@
         <v>3.9050000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -2378,7 +2451,7 @@
         <v>1.7569999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1</v>
       </c>
@@ -2411,7 +2484,7 @@
         <v>3.6560000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1</v>
       </c>
@@ -2444,7 +2517,7 @@
         <v>2.5872000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1</v>
       </c>
@@ -2477,7 +2550,7 @@
         <v>5.9390000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1</v>
       </c>
@@ -2510,7 +2583,7 @@
         <v>6.7129999999999992</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1</v>
       </c>
@@ -2764,6 +2837,9 @@
       </c>
       <c r="L24" s="49" t="s">
         <v>215</v>
+      </c>
+      <c r="M24" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
@@ -3530,6 +3606,7 @@
     <hyperlink ref="L18" r:id="rId40" xr:uid="{09BA8893-4495-41E7-88F8-697E23A9411C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -3554,39 +3631,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="100" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="104" t="s">
+      <c r="B1" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="102" t="s">
+      <c r="D1" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="102" t="s">
+      <c r="E1" s="110" t="s">
         <v>99</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="108" t="s">
         <v>120</v>
       </c>
-      <c r="G1" s="108" t="s">
+      <c r="G1" s="102" t="s">
         <v>132</v>
       </c>
       <c r="H1" s="112"/>
-      <c r="I1" s="110" t="s">
+      <c r="I1" s="104" t="s">
         <v>134</v>
       </c>
-      <c r="J1" s="111"/>
-      <c r="K1" s="98" t="s">
+      <c r="J1" s="105"/>
+      <c r="K1" s="106" t="s">
         <v>133</v>
       </c>
-      <c r="L1" s="99"/>
+      <c r="L1" s="107"/>
     </row>
     <row r="2" spans="1:25" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="107"/>
+      <c r="A2" s="101"/>
       <c r="B2" s="113"/>
       <c r="C2" s="114"/>
       <c r="D2" s="114"/>
@@ -5343,4 +5420,158 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5673A395-CBE6-40D4-87FC-F1A8F9554773}">
+  <dimension ref="A2:F10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5">
+        <v>20</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>264</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6">
+        <v>20</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://www.mouser.pl/ProductDetail/Molex/46765-0301?qs=bpeZmj96Seed20dZhMSXqw%3D%3D" xr:uid="{073EBA41-AC5A-40F9-8363-2E27B7386BCD}"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://www.mouser.pl/ProductDetail/Raspberry-Pi/SC0358?qs=sGAEpiMZZMsvnOgGvSjZeHfx0dldyM%2Fty40t4MMDEBqB8FZUAXZoPQ%3D%3D" xr:uid="{C4019E9A-1E3A-40BD-B842-BE6180D7E352}"/>
+    <hyperlink ref="C6" r:id="rId3" xr:uid="{43E18FEA-033F-46EC-A684-A32250D00792}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{A2F2DD76-8F39-45B7-9B8C-DFF6651F71D7}"/>
+    <hyperlink ref="C8" r:id="rId5" xr:uid="{71C3B908-2430-4BDC-ACF3-C948C9CFFF4A}"/>
+    <hyperlink ref="C9" r:id="rId6" xr:uid="{D155872E-3D18-42CD-ADEF-3340CF9476F6}"/>
+    <hyperlink ref="C10" r:id="rId7" xr:uid="{322E6D2C-5234-40B8-8936-7C647FDB3076}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM_Drone_Board\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD108B92-E698-4CEB-89CB-2782784DAF2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5624364-F3A0-4C0A-B5C5-254C646C17AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="4" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
